--- a/files/九龙-何文田-天铸 (第2期).xlsx
+++ b/files/九龙-何文田-天铸 (第2期).xlsx
@@ -3059,7 +3059,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -13776,7 +13776,7 @@
           <t>B | 1823呎 (4+房)
 $4,234万
 $23,227/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D19" s="18" t="inlineStr">

--- a/files/九龙-何文田-天铸 (第2期).xlsx
+++ b/files/九龙-何文田-天铸 (第2期).xlsx
@@ -8,10 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座 销控表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座 销控表" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -114,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -179,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -195,45 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -943,7 +807,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2016-05-08</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -989,7 +853,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2016-05-12</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1219,7 +1083,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1265,7 +1129,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-04-03</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1311,7 +1175,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-05</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1403,7 +1267,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-20</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1495,7 +1359,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2016-05-09</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1541,7 +1405,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2016-04-28</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1587,7 +1451,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-03</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1633,7 +1497,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-05</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1679,7 +1543,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-15</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1725,7 +1589,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-15</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1771,7 +1635,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-08</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1817,7 +1681,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-02</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1863,7 +1727,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-11</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1909,7 +1773,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -1955,7 +1819,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2001,7 +1865,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-04-03</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2047,7 +1911,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2093,7 +1957,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-02</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2139,7 +2003,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2185,7 +2049,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-09-22</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2231,7 +2095,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2277,7 +2141,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-02</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2323,7 +2187,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-10</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2369,7 +2233,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-04-09</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2415,7 +2279,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-09</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2461,7 +2325,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2553,7 +2417,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-09</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2599,7 +2463,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2645,7 +2509,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-28</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2691,7 +2555,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-04</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2737,7 +2601,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-25</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2783,7 +2647,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-09</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2829,7 +2693,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-05</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2875,7 +2739,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2921,7 +2785,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -2967,7 +2831,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-12</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3013,7 +2877,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-28</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3059,7 +2923,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3105,7 +2969,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3151,7 +3015,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-12</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3197,7 +3061,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-12</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3335,7 +3199,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-09</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3381,7 +3245,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-24</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3427,7 +3291,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-08</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3473,7 +3337,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-18</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3565,7 +3429,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3611,7 +3475,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-03</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3657,7 +3521,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-25</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3749,7 +3613,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3795,7 +3659,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-19</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3841,7 +3705,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-19</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3979,7 +3843,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-17</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4025,7 +3889,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-17</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4071,7 +3935,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4117,7 +3981,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2016-05-05</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4163,7 +4027,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-12</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4255,7 +4119,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-03-03</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4347,7 +4211,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-17</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4439,7 +4303,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2016-05-08</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4485,7 +4349,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-19</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4531,7 +4395,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-17</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4577,7 +4441,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-17</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4715,7 +4579,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-17</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4761,7 +4625,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-17</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4807,7 +4671,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-11</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4853,7 +4717,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-19</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -4899,7 +4763,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-19</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -4945,7 +4809,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-19</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -4991,7 +4855,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5037,7 +4901,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5083,7 +4947,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-19</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5175,7 +5039,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5221,7 +5085,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-02-17</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5267,7 +5131,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-18</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5359,7 +5223,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-18</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5405,7 +5269,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2016-05-22</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5451,7 +5315,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2016-05-03</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5497,7 +5361,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5543,7 +5407,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-19</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5589,7 +5453,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-28</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5635,7 +5499,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -5681,7 +5545,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5727,7 +5591,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -5773,7 +5637,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -5819,7 +5683,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2016-04-18</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -5865,7 +5729,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-13</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -5911,7 +5775,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-14</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -5957,7 +5821,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-14</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -6003,7 +5867,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-25</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6049,7 +5913,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2016-05-04</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6095,7 +5959,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-19</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6141,7 +6005,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6187,7 +6051,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -6233,7 +6097,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -6279,7 +6143,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -6325,7 +6189,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-18</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6371,7 +6235,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-08</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -6417,7 +6281,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-05</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -6463,7 +6327,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-18</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6509,7 +6373,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -6555,7 +6419,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -6601,7 +6465,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6647,7 +6511,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2016-04-18</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -6739,7 +6603,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -6785,7 +6649,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-03</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -6877,7 +6741,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-15</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -6923,7 +6787,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -7015,7 +6879,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-02-20</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7061,7 +6925,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-07-29</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -7107,7 +6971,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -7199,7 +7063,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-24</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -7245,7 +7109,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-02-25</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -7291,7 +7155,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -7337,7 +7201,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -7383,7 +7247,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -7429,7 +7293,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-01-30</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -7475,7 +7339,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -7521,7 +7385,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -7567,7 +7431,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-09</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -7613,7 +7477,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-01-24</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -7659,7 +7523,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-08</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -7705,7 +7569,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2016-05-03</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -7843,7 +7707,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -7889,7 +7753,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -7935,7 +7799,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -7981,7 +7845,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -8027,7 +7891,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-18</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -8073,7 +7937,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2016-04-25</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -8119,7 +7983,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-15</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -8165,7 +8029,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-01-20</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -8211,7 +8075,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -8257,7 +8121,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-28</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -8303,7 +8167,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-28</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -8349,7 +8213,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-01-17</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -8395,7 +8259,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -8441,7 +8305,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-12</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -8487,7 +8351,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-24</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -8533,7 +8397,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2016-05-08</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -8579,7 +8443,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-04</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -8625,7 +8489,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-04</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -8671,7 +8535,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -8717,7 +8581,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-01-21</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -8763,7 +8627,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-25</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -8809,7 +8673,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-19</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -8855,7 +8719,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-02</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -8947,7 +8811,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -8993,7 +8857,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-25</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -9131,7 +8995,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-24</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -9177,7 +9041,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-24</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -9223,7 +9087,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -9269,7 +9133,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-01-31</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -9315,7 +9179,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-19</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -9361,7 +9225,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-19</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -9407,7 +9271,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -9453,7 +9317,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -9499,7 +9363,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2016-04-19</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -9545,7 +9409,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-18</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -9591,7 +9455,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-19</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -9637,7 +9501,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-01-14</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -9683,7 +9547,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -9729,7 +9593,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -9775,7 +9639,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -9821,7 +9685,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-03</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -9959,7 +9823,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-02-14</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -10005,7 +9869,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-02-20</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -10051,7 +9915,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -10097,7 +9961,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-08</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -10143,7 +10007,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -10189,7 +10053,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -10235,7 +10099,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-04</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -10281,7 +10145,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-12</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -10327,7 +10191,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -10373,7 +10237,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-01-30</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -10419,7 +10283,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-28</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -10465,7 +10329,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-11</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -10511,7 +10375,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-11</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -10557,7 +10421,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-01-14</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -10649,7 +10513,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-28</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -10787,7 +10651,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-08</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -10833,7 +10697,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -10879,7 +10743,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -10925,7 +10789,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-01-06</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -10971,7 +10835,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-08</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -11017,7 +10881,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-12</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -11063,7 +10927,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-12</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -11109,7 +10973,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-01-16</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -11155,7 +11019,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -11201,7 +11065,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-04</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -11247,7 +11111,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-15</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -11293,7 +11157,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-01-16</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -11339,7 +11203,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-12</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -11385,7 +11249,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-05</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -11431,7 +11295,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2016-05-12</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -11477,7 +11341,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-01-06</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -11523,7 +11387,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -11569,7 +11433,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-04</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -11615,7 +11479,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-11</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -11661,7 +11525,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-01-16</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -11707,7 +11571,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -11753,7 +11617,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -11799,7 +11663,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -11845,7 +11709,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-08</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -11891,7 +11755,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-28</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -11937,7 +11801,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -11983,7 +11847,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-11</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -12029,7 +11893,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-09</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -12121,7 +11985,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-11</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -12167,7 +12031,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -12213,7 +12077,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2016-05-19</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -12259,7 +12123,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-02</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -12305,7 +12169,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-15</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -12351,7 +12215,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -12397,7 +12261,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-01-15</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -12443,7 +12307,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-28</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -12489,7 +12353,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-09</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -12535,7 +12399,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-15</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -12581,7 +12445,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2019-01-03</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -12627,7 +12491,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -12719,7 +12583,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2016-05-15</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -12765,7 +12629,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2016-05-12</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -12811,7 +12675,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -12857,7 +12721,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-18</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -12903,7 +12767,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-15</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -12949,7 +12813,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-15</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -12995,7 +12859,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -13087,7 +12951,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-05-18</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -13155,3207 +13019,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天铸 (第2期) - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>63 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>61 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>23&amp;25/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 2866呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 2503呎 (4+房)
-$8,719万
-$34,834/呎
-(16年-04月)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>21&amp;22/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 2493呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 2442呎 (4+房)
-$13,076万
-$53,546/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 2489呎 (4+房)
-$10,247万
-$41,169/呎
-(16年-04月)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 1910呎 (4+房)
-$7,752万
-$40,584/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 1731呎 (4+房)
-$7,478万
-$43,203/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 1154呎 (3房)
-$3,469万
-$30,058/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 994呎 (3房)
-$2,977万
-$29,953/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 1910呎 (4+房)
-$8,480万
-$44,397/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 1823呎 (4+房)
-$9,466万
-$51,927/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 1154呎 (3房)
-$6,396万
-$55,425/呎
-(16年-04月)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 994呎 (3房)
-$6,396万
-$64,346/呎
-(16年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 1910呎 (4+房)
-$7,227万
-$37,837/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 1731呎 (4+房)
-$7,854万
-$45,373/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 1154呎 (3房)
-$3,377万
-$29,263/呎
-(16年-04月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 994呎 (3房)
-$2,968万
-$29,863/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 1910呎 (4+房)
-$8,610万
-$45,078/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 1731呎 (4+房)
-$7,754万
-$44,794/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 1154呎 (3房)
-$3,364万
-$29,146/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 994呎 (3房)
-$2,951万
-$29,685/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 1910呎 (4+房)
-$8,572万
-$44,880/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 1823呎 (4+房)
-$8,529万
-$46,787/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 1154呎 (3房)
-$3,357万
-$29,088/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 994呎 (3房)
-$2,942万
-$29,596/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 1910呎 (4+房)
-$7,672万
-$40,169/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 1823呎 (4+房)
-$8,333万
-$45,711/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 1154呎 (3房)
-$3,347万
-$29,001/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 994呎 (3房)
-$2,933万
-$29,507/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 2019呎 (4+房)
-$8,076万
-$40,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 1823呎 (4+房)
-$7,295万
-$40,018/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 1154呎 (3房)
-$3,286万
-$28,479/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 994呎 (3房)
-$2,895万
-$29,124/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 1910呎 (4+房)
-$8,087万
-$42,338/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 1823呎 (4+房)
-$6,927万
-$38,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 1154呎 (3房)
-$3,211万
-$27,824/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 994呎 (3房)
-$2,857万
-$28,745/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 2019呎 (4+房)
-$7,207万
-$35,698/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 1823呎 (4+房)
-$15,180万
-$83,269/呎
-(16年-04月)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 1154呎 (3房)
-$3,137万
-$27,184/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 994呎 (3房)
-$2,792万
-$28,084/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 2019呎 (4+房)
-$5,588万
-$27,679/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 1823呎 (4+房)
-$5,001万
-$27,433/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 1154呎 (3房)
-$3,008万
-$26,069/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 994呎 (3房)
-$2,705万
-$27,213/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 1910呎 (4+房)
-$5,588万
-$29,257/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 1823呎 (4+房)
-$5,001万
-$27,435/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 1154呎 (3房)
-$2,858万
-$24,766/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 994呎 (3房)
-$2,637万
-$26,533/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 2019呎 (4+房)
-$4,703万
-$23,292/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 1823呎 (4+房)
-$4,234万
-$23,227/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 1154呎 (3房)
-$2,741万
-$23,751/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 994呎 (3房)
-$2,529万
-$25,445/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 2019呎 (4+房)
-$6,379万
-$31,596/呎
-(16年-03月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 1823呎 (4+房)
-$6,379万
-$34,993/呎
-(16年-03月)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 1154呎 (3房)
-$2,289万
-$19,832/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 994呎 (3房)
-$2,036万
-$20,483/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 2019呎 (4+房)
-$3,613万
-$17,895/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 1807呎 (4+房)
-$3,006万
-$16,637/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 1045呎 (3房)
-$2,070万
-$19,812/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 863呎 (3房)
-$1,833万
-$21,235/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>3&amp;4/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 2065呎 (3房)
-$4,674万
-$22,634/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 2337呎 (4+房)
-$5,436万
-$23,262/呎
-(16年-04月)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr"/>
-      <c r="E22" s="17" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天铸 (第2期) - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>68 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>68 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>25&amp;26/F</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>A | 2681呎 (4+房)
-$14,831万
-$55,319/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 2079呎 (3房)
-$7,509万
-$36,121/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 2090呎 (3房)
-$7,751万
-$37,088/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr"/>
-      <c r="C7" s="17" t="inlineStr"/>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 2026呎 (4+房)
-$8,348万
-$41,206/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr"/>
-      <c r="C8" s="17" t="inlineStr"/>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 1428呎 (4+房)
-$4,207万
-$29,461/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 1237呎 (3房)
-$3,534万
-$28,573/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>22&amp;23/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 2199呎 (4+房)
-$11,391万
-$51,801/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 2361呎 (4+房)
-$12,169万
-$51,540/呎
-(16年-04月)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr"/>
-      <c r="E9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 1738呎 (4+房)
-$7,820万
-$44,994/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 1606呎 (4+房)
-$7,198万
-$44,819/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 1428呎 (4+房)
-$4,194万
-$29,373/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 1237呎 (3房)
-$3,527万
-$28,516/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 1646呎 (4+房)
-$8,182万
-$49,711/呎
-(19年-01月)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 1606呎 (4+房)
-$7,464万
-$46,475/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 1428呎 (4+房)
-$8,351万
-$58,483/呎
-(16年-03月)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 1237呎 (3房)
-$3,520万
-$28,459/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 1738呎 (4+房)
-$7,583万
-$43,633/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 1708呎 (4+房)
-$6,946万
-$40,665/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 1428呎 (4+房)
-$8,351万
-$58,483/呎
-(16年-03月)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 1237呎 (3房)
-$3,513万
-$28,402/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 1646呎 (4+房)
-$6,398万
-$38,870/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 1606呎 (4+房)
-$7,068万
-$44,010/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 1428呎 (4+房)
-$4,169万
-$29,198/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 1237呎 (3房)
-$3,513万
-$28,402/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 1738呎 (4+房)
-$7,318万
-$42,104/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 1708呎 (4+房)
-$6,735万
-$39,433/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 1428呎 (4+房)
-$4,145万
-$29,024/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 1237呎 (3房)
-$3,499万
-$28,289/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 1738呎 (4+房)
-$7,188万
-$41,360/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 1708呎 (4+房)
-$6,649万
-$38,927/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 1428呎 (4+房)
-$4,132万
-$28,937/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 1237呎 (3房)
-$3,492万
-$28,233/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 1646呎 (4+房)
-$7,911万
-$48,062/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 1606呎 (4+房)
-$6,829万
-$42,522/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 1428呎 (4+房)
-$8,145万
-$57,036/呎
-(16年-03月)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 1142呎 (3房)
-$3,482万
-$30,490/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 1738呎 (4+房)
-$6,652万
-$38,276/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 1708呎 (4+房)
-$6,410万
-$37,530/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 1428呎 (4+房)
-$8,145万
-$57,036/呎
-(16年-03月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 1142呎 (3房)
-$3,419万
-$29,941/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 1738呎 (4+房)
-$6,167万
-$35,482/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 1708呎 (4+房)
-$5,942万
-$34,790/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 1428呎 (4+房)
-$3,892万
-$27,256/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 1237呎 (3房)
-$3,306万
-$26,729/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 1738呎 (4+房)
-$5,080万
-$29,231/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 1708呎 (4+房)
-$4,914万
-$28,771/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 1428呎 (4+房)
-$3,764万
-$26,357/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 1237呎 (3房)
-$3,197万
-$25,847/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 1738呎 (4+房)
-$4,288万
-$24,671/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 1708呎 (4+房)
-$4,197万
-$24,571/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 1428呎 (4+房)
-$3,666万
-$25,672/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 1237呎 (3房)
-$3,114万
-$25,175/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 1738呎 (4+房)
-$4,159万
-$23,931/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 1708呎 (4+房)
-$4,071万
-$23,833/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 1428呎 (4+房)
-$3,593万
-$25,158/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 1237呎 (3房)
-$3,036万
-$24,546/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 1738呎 (4+房)
-$3,989万
-$22,950/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 1708呎 (4+房)
-$3,904万
-$22,856/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 1428呎 (4+房)
-$3,409万
-$23,875/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 1237呎 (3房)
-$2,881万
-$23,294/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 1738呎 (4+房)
-$3,206万
-$18,449/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 1708呎 (4+房)
-$2,903万
-$16,996/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 1428呎 (4+房)
-$2,617万
-$18,328/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 1237呎 (3房)
-$2,320万
-$18,752/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 1630呎 (4+房)
-$3,503万
-$21,490/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 1691呎 (4+房)
-$2,905万
-$17,177/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 1324呎 (4+房)
-$2,597万
-$19,615/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 1221呎 (3房)
-$2,113万
-$17,309/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天铸 (第2期) - 3座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>68 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>68 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>25&amp;26/F</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>A | 2681呎 (4+房)
-$15,227万
-$56,795/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 1990呎 (3房)
-$12,540万
-$63,015/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 2173呎 (3房)
-$7,670万
-$35,298/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr"/>
-      <c r="C7" s="17" t="inlineStr"/>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 2128呎 (3房)
-$8,248万
-$38,761/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr"/>
-      <c r="C8" s="17" t="inlineStr"/>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3,250万
-$26,273/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$4,251万
-$29,770/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>22&amp;23/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 2265呎 (4+房)
-$15,583万
-$68,797/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 2199呎 (4+房)
-$14,260万
-$64,849/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr"/>
-      <c r="E9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$7,567万
-$44,304/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$6,650万
-$38,262/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$7,133万
-$57,666/呎
-(16年-03月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$4,238万
-$29,681/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$7,472万
-$43,746/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$6,532万
-$37,585/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3,556万
-$28,747/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$4,226万
-$29,592/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$6,764万
-$39,600/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$6,417万
-$36,921/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3,549万
-$28,689/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$4,213万
-$29,503/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$13,498万
-$79,030/呎
-(16年-04月)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$13,498万
-$77,666/呎
-(16年-04月)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3,549万
-$28,689/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$4,213万
-$29,503/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$6,662万
-$39,006/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$6,192万
-$35,627/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3,535万
-$28,575/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$4,188万
-$29,328/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$6,663万
-$39,009/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$6,082万
-$34,997/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3,528万
-$28,518/呎
-(23年-07月)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$4,175万
-$29,240/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$6,483万
-$37,957/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$6,064万
-$34,892/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3,517万
-$28,432/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$4,163万
-$29,152/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$6,290万
-$36,827/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$5,864万
-$33,740/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3,454万
-$27,921/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$4,067万
-$28,482/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$5,890万
-$34,483/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$5,436万
-$31,277/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3,340万
-$26,999/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$3,933万
-$27,542/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$5,567万
-$32,593/呎
-(19年-03月)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$4,441万
-$25,554/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3,263万
-$26,378/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$3,842万
-$26,908/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$8,063万
-$47,206/呎
-(16年-03月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$8,063万
-$46,391/呎
-(16年-03月)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3,178万
-$25,692/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$3,743万
-$26,209/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$5,332万
-$31,220/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$3,891万
-$22,388/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3,115万
-$25,179/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$3,630万
-$25,422/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$5,188万
-$30,378/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$3,790万
-$21,806/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$2,800万
-$22,635/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$3,227万
-$22,600/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$5,049万
-$29,560/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$3,127万
-$17,990/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$2,082万
-$16,831/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$2,499万
-$17,500/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 1691呎 (4+房)
-$3,166万
-$18,724/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 1722呎 (4+房)
-$3,061万
-$17,778/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 1221呎 (3房)
-$2,198万
-$18,005/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 1412呎 (4+房)
-$2,421万
-$17,145/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天铸 (第2期) - 5座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>72 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>72 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>25&amp;26/F</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>A | 2733呎 (4+房)
-$21,391万
-$78,270/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 2130呎 (4+房)
-$9,165万
-$43,028/呎
-(16年-04月)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 2187呎 (4+房)
-$15,180万
-$69,410/呎
-(16年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 1320呎 (4+房)
-$4,308万
-$32,634/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 1316呎 (4+房)
-$3,998万
-$30,381/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 2044呎 (3房)
-$12,860万
-$62,916/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 1320呎 (4+房)
-$4,295万
-$32,535/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 1221呎 (4+房)
-$3,947万
-$32,325/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 1723呎 (4+房)
-$7,074万
-$41,056/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 1160呎 (3房)
-$3,862万
-$33,292/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 1320呎 (4+房)
-$4,273万
-$32,373/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 1221呎 (4+房)
-$3,896万
-$31,910/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 1723呎 (4+房)
-$7,144万
-$41,465/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 1160呎 (3房)
-$3,841万
-$33,110/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 1320呎 (4+房)
-$4,190万
-$31,739/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 1316呎 (4+房)
-$7,643万
-$58,079/呎
-(16年-04月)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 1723呎 (4+房)
-$6,358万
-$36,904/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 1160呎 (3房)
-$3,820万
-$32,929/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 1320呎 (4+房)
-$4,196万
-$31,792/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 1316呎 (4+房)
-$3,797万
-$28,851/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 1723呎 (4+房)
-$5,342万
-$31,006/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 1160呎 (3房)
-$7,643万
-$65,889/呎
-(16年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 1320呎 (4+房)
-$4,155万
-$31,477/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 1316呎 (4+房)
-$3,759万
-$28,566/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 1723呎 (4+房)
-$6,268万
-$36,377/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 1160呎 (3房)
-$3,782万
-$32,601/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 1320呎 (4+房)
-$4,011万
-$30,383/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 1221呎 (4+房)
-$3,700万
-$30,303/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 1723呎 (4+房)
-$6,451万
-$37,442/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 1160呎 (3房)
-$3,653万
-$31,491/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 1320呎 (4+房)
-$3,940万
-$29,846/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 1316呎 (4+房)
-$3,653万
-$27,755/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 1723呎 (4+房)
-$6,802万
-$39,477/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 1160呎 (3房)
-$3,540万
-$30,514/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 1320呎 (4+房)
-$3,928万
-$29,756/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 1316呎 (4+房)
-$3,642万
-$27,672/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 1723呎 (4+房)
-$5,814万
-$33,745/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 1065呎 (3房)
-$3,529万
-$33,136/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 1320呎 (4+房)
-$3,837万
-$29,072/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 1316呎 (4+房)
-$3,576万
-$27,174/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 1723呎 (4+房)
-$5,815万
-$33,750/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 1160呎 (3房)
-$3,501万
-$30,179/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 1320呎 (4+房)
-$3,711万
-$28,112/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 1316呎 (4+房)
-$3,512万
-$26,685/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 1723呎 (4+房)
-$5,663万
-$32,869/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 1160呎 (3房)
-$3,403万
-$29,337/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 1320呎 (4+房)
-$3,477万
-$26,341/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 1221呎 (4+房)
-$3,361万
-$27,524/呎
-(16年-04月)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 1723呎 (4+房)
-$5,448万
-$31,620/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 1065呎 (3房)
-$3,308万
-$31,060/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 1320呎 (4+房)
-$3,317万
-$25,130/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 1316呎 (4+房)
-$3,139万
-$23,852/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 1723呎 (4+房)
-$5,279万
-$30,640/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 1160呎 (3房)
-$3,156万
-$27,204/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 1320呎 (4+房)
-$3,085万
-$23,371/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 1316呎 (4+房)
-$2,919万
-$22,182/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 1723呎 (4+房)
-$5,534万
-$32,120/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 1065呎 (3房)
-$3,045万
-$28,596/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 1320呎 (4+房)
-$3,066万
-$23,230/呎
-(16年-04月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 1316呎 (4+房)
-$2,902万
-$22,049/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 1723呎 (4+房)
-$4,871万
-$28,272/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 1160呎 (3房)
-$2,875万
-$24,784/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 1320呎 (4+房)
-$2,529万
-$19,162/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 1221呎 (4+房)
-$2,211万
-$18,105/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 1723呎 (4+房)
-$3,896万
-$22,610/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 1160呎 (3房)
-$2,329万
-$20,075/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 1150呎 (4+房)
-$3,623万
-$31,505/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 1300呎 (4+房)
-$2,506万
-$19,276/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 1723呎 (3房)
-$3,909万
-$22,690/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 1143呎 (3房)
-$2,173万
-$19,011/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>3&amp;4/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 1929呎 (3房)
-$4,593万
-$23,811/呎
-(16年-04月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 1970呎 (2房)
-$6,277万
-$31,865/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr"/>
-      <c r="E24" s="17" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-何文田-天铸 (第2期).xlsx
+++ b/files/九龙-何文田-天铸 (第2期).xlsx
@@ -8,6 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +45,90 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +139,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +220,57 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +647,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -13019,4 +13192,3207 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>23&amp;25</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 2866呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 2503呎 (4+房)
+$8719万
+$34,834/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>21&amp;22</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2493呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 2442呎 (4+房)
+$13076万
+$53,546/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 2489呎 (4+房)
+$10247万
+$41,169/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 1910呎 (4+房)
+$7752万
+$40,584/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 1731呎 (4+房)
+$7478万
+$43,203/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 1154呎 (3房)
+$3469万
+$30,058/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 994呎 (3房)
+$2977万
+$29,953/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 1910呎 (4+房)
+$8480万
+$44,397/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 1823呎 (4+房)
+$9466万
+$51,927/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 1154呎 (3房)
+$6396万
+$55,425/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 994呎 (3房)
+$6396万
+$64,346/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 1910呎 (4+房)
+$7227万
+$37,837/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 1731呎 (4+房)
+$7854万
+$45,373/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 1154呎 (3房)
+$3377万
+$29,263/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 994呎 (3房)
+$2968万
+$29,863/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1910呎 (4+房)
+$8610万
+$45,078/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 1731呎 (4+房)
+$7754万
+$44,794/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 1154呎 (3房)
+$3364万
+$29,146/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 994呎 (3房)
+$2951万
+$29,685/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1910呎 (4+房)
+$8572万
+$44,880/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 1823呎 (4+房)
+$8529万
+$46,787/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 1154呎 (3房)
+$3357万
+$29,088/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 994呎 (3房)
+$2942万
+$29,596/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1910呎 (4+房)
+$7672万
+$40,169/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 1823呎 (4+房)
+$8333万
+$45,711/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 1154呎 (3房)
+$3347万
+$29,001/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 994呎 (3房)
+$2933万
+$29,507/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 2019呎 (4+房)
+$8076万
+$40,000/呎
+(19年-09月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1823呎 (4+房)
+$7295万
+$40,018/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 1154呎 (3房)
+$3286万
+$28,479/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 994呎 (3房)
+$2895万
+$29,124/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1910呎 (4+房)
+$8087万
+$42,338/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1823呎 (4+房)
+$6927万
+$38,000/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 1154呎 (3房)
+$3211万
+$27,824/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 994呎 (3房)
+$2857万
+$28,745/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 2019呎 (4+房)
+$7207万
+$35,698/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 1823呎 (4+房)
+$15180万
+$83,269/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 1154呎 (3房)
+$3137万
+$27,184/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 994呎 (3房)
+$2792万
+$28,084/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 2019呎 (4+房)
+$5588万
+$27,679/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 1823呎 (4+房)
+$5001万
+$27,433/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 1154呎 (3房)
+$3008万
+$26,069/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 994呎 (3房)
+$2705万
+$27,213/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 1910呎 (4+房)
+$5588万
+$29,257/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 1823呎 (4+房)
+$5001万
+$27,435/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 1154呎 (3房)
+$2858万
+$24,766/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 994呎 (3房)
+$2637万
+$26,533/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 2019呎 (4+房)
+$4703万
+$23,292/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 1823呎 (4+房)
+$4234万
+$23,227/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 1154呎 (3房)
+$2741万
+$23,751/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 994呎 (3房)
+$2529万
+$25,445/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 2019呎 (4+房)
+$6379万
+$31,596/呎
+(16年-03月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 1823呎 (4+房)
+$6379万
+$34,993/呎
+(16年-03月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 1154呎 (3房)
+$2289万
+$19,832/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 994呎 (3房)
+$2036万
+$20,483/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 2019呎 (4+房)
+$3613万
+$17,895/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 1807呎 (4+房)
+$3006万
+$16,637/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 1045呎 (3房)
+$2070万
+$19,812/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 863呎 (3房)
+$1833万
+$21,235/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>3&amp;4</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 2065呎 (3房)
+$4674万
+$22,634/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 2337呎 (4+房)
+$5436万
+$23,262/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr"/>
+      <c r="E21" s="21" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 2681呎 (4+房)
+$14831万
+$55,319/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 2079呎 (3房)
+$7509万
+$36,121/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 2090呎 (3房)
+$7751万
+$37,088/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 2026呎 (4+房)
+$8348万
+$41,206/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>22&amp;23</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 2199呎 (4+房)
+$11391万
+$51,801/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 2361呎 (4+房)
+$12169万
+$51,540/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr"/>
+      <c r="C8" s="21" t="inlineStr"/>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 1428呎 (4+房)
+$4207万
+$29,461/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 1237呎 (3房)
+$3534万
+$28,573/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 1738呎 (4+房)
+$7820万
+$44,994/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 1606呎 (4+房)
+$7198万
+$44,819/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 1428呎 (4+房)
+$4194万
+$29,373/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 1237呎 (3房)
+$3527万
+$28,516/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1646呎 (4+房)
+$8182万
+$49,711/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 1606呎 (4+房)
+$7464万
+$46,475/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 1428呎 (4+房)
+$8351万
+$58,483/呎
+(16年-03月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 1237呎 (3房)
+$3520万
+$28,459/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1738呎 (4+房)
+$7583万
+$43,633/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 1708呎 (4+房)
+$6946万
+$40,665/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 1428呎 (4+房)
+$8351万
+$58,483/呎
+(16年-03月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 1237呎 (3房)
+$3513万
+$28,402/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1646呎 (4+房)
+$6398万
+$38,870/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 1606呎 (4+房)
+$7068万
+$44,010/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 1428呎 (4+房)
+$4169万
+$29,198/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 1237呎 (3房)
+$3513万
+$28,402/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1738呎 (4+房)
+$7318万
+$42,104/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1708呎 (4+房)
+$6735万
+$39,433/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 1428呎 (4+房)
+$4145万
+$29,024/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 1237呎 (3房)
+$3499万
+$28,289/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1738呎 (4+房)
+$7188万
+$41,360/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1708呎 (4+房)
+$6649万
+$38,927/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 1428呎 (4+房)
+$4132万
+$28,937/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 1237呎 (3房)
+$3492万
+$28,233/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 1646呎 (4+房)
+$7911万
+$48,062/呎
+(19年-02月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 1606呎 (4+房)
+$6829万
+$42,522/呎
+(19年-08月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 1428呎 (4+房)
+$8145万
+$57,036/呎
+(16年-03月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 1142呎 (3房)
+$3482万
+$30,490/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 1738呎 (4+房)
+$6652万
+$38,276/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 1708呎 (4+房)
+$6410万
+$37,530/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 1428呎 (4+房)
+$8145万
+$57,036/呎
+(16年-03月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 1142呎 (3房)
+$3419万
+$29,941/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 1738呎 (4+房)
+$6167万
+$35,482/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 1708呎 (4+房)
+$5942万
+$34,790/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 1428呎 (4+房)
+$3892万
+$27,256/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 1237呎 (3房)
+$3306万
+$26,729/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 1738呎 (4+房)
+$5080万
+$29,231/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 1708呎 (4+房)
+$4914万
+$28,771/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 1428呎 (4+房)
+$3764万
+$26,357/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 1237呎 (3房)
+$3197万
+$25,847/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 1738呎 (4+房)
+$4288万
+$24,671/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 1708呎 (4+房)
+$4197万
+$24,571/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 1428呎 (4+房)
+$3666万
+$25,672/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 1237呎 (3房)
+$3114万
+$25,175/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 1738呎 (4+房)
+$4159万
+$23,931/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 1708呎 (4+房)
+$4071万
+$23,833/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 1428呎 (4+房)
+$3593万
+$25,158/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 1237呎 (3房)
+$3036万
+$24,546/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 1738呎 (4+房)
+$3989万
+$22,950/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 1708呎 (4+房)
+$3904万
+$22,856/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 1428呎 (4+房)
+$3409万
+$23,875/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 1237呎 (3房)
+$2881万
+$23,294/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 1738呎 (4+房)
+$3206万
+$18,449/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 1708呎 (4+房)
+$2903万
+$16,996/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 1428呎 (4+房)
+$2617万
+$18,328/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 1237呎 (3房)
+$2320万
+$18,752/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 1630呎 (4+房)
+$3503万
+$21,490/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 1691呎 (4+房)
+$2905万
+$17,177/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 1324呎 (4+房)
+$2597万
+$19,615/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 1221呎 (3房)
+$2113万
+$17,309/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 2681呎 (4+房)
+$15227万
+$56,795/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 1990呎 (3房)
+$12540万
+$63,015/呎
+(19年-11月)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 2173呎 (3房)
+$7670万
+$35,298/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 2128呎 (3房)
+$8248万
+$38,761/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>22&amp;23</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 2265呎 (4+房)
+$15583万
+$68,797/呎
+(19年-07月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 2199呎 (4+房)
+$14260万
+$64,849/呎
+(19年-02月)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr"/>
+      <c r="C8" s="21" t="inlineStr"/>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3250万
+$26,273/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$4251万
+$29,770/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$7567万
+$44,304/呎
+(19年-02月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$6650万
+$38,262/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$7133万
+$57,666/呎
+(16年-03月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$4238万
+$29,681/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$7472万
+$43,746/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$6532万
+$37,585/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3556万
+$28,747/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$4226万
+$29,592/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$6764万
+$39,600/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$6417万
+$36,921/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3549万
+$28,689/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$4213万
+$29,503/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$13498万
+$79,030/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$13498万
+$77,666/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3549万
+$28,689/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$4213万
+$29,503/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$6662万
+$39,006/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$6192万
+$35,627/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3535万
+$28,575/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$4188万
+$29,328/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$6663万
+$39,009/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$6082万
+$34,997/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3528万
+$28,518/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$4175万
+$29,240/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$6483万
+$37,957/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$6064万
+$34,892/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3517万
+$28,432/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$4163万
+$29,152/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$6290万
+$36,827/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$5864万
+$33,740/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3454万
+$27,921/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$4067万
+$28,482/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$5890万
+$34,483/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$5436万
+$31,277/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3340万
+$26,999/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$3933万
+$27,542/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$5567万
+$32,593/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$4441万
+$25,554/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3263万
+$26,378/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$3842万
+$26,908/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$8063万
+$47,206/呎
+(16年-03月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$8063万
+$46,391/呎
+(16年-03月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3178万
+$25,692/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$3743万
+$26,209/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$5332万
+$31,220/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$3891万
+$22,388/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3115万
+$25,179/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$3630万
+$25,422/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$5188万
+$30,378/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$3790万
+$21,806/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$2800万
+$22,635/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$3227万
+$22,600/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$5049万
+$29,560/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$3127万
+$17,990/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$2082万
+$16,831/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$2499万
+$17,500/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 1691呎 (4+房)
+$3166万
+$18,724/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 1722呎 (4+房)
+$3061万
+$17,778/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 1221呎 (3房)
+$2198万
+$18,005/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 1412呎 (4+房)
+$2421万
+$17,145/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 2733呎 (4+房)
+$21391万
+$78,270/呎
+(19年-02月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 2130呎 (4+房)
+$9165万
+$43,028/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 2187呎 (4+房)
+$15180万
+$69,410/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 1320呎 (4+房)
+$4308万
+$32,634/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 1316呎 (4+房)
+$3998万
+$30,381/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 2044呎 (3房)
+$12860万
+$62,916/呎
+(20年-02月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 1320呎 (4+房)
+$4295万
+$32,535/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 1221呎 (4+房)
+$3947万
+$32,325/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 1723呎 (4+房)
+$7074万
+$41,056/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 1160呎 (3房)
+$3862万
+$33,292/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 1320呎 (4+房)
+$4273万
+$32,373/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 1221呎 (4+房)
+$3896万
+$31,910/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 1723呎 (4+房)
+$7144万
+$41,465/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 1160呎 (3房)
+$3841万
+$33,110/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 1320呎 (4+房)
+$4190万
+$31,739/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 1316呎 (4+房)
+$7643万
+$58,079/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 1723呎 (4+房)
+$6358万
+$36,904/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 1160呎 (3房)
+$3820万
+$32,929/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1320呎 (4+房)
+$4196万
+$31,792/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 1316呎 (4+房)
+$3797万
+$28,851/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 1723呎 (4+房)
+$5342万
+$31,006/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 1160呎 (3房)
+$7643万
+$65,889/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1320呎 (4+房)
+$4155万
+$31,477/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 1316呎 (4+房)
+$3759万
+$28,566/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 1723呎 (4+房)
+$6268万
+$36,377/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 1160呎 (3房)
+$3782万
+$32,601/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1320呎 (4+房)
+$4011万
+$30,383/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 1221呎 (4+房)
+$3700万
+$30,303/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 1723呎 (4+房)
+$6451万
+$37,442/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 1160呎 (3房)
+$3653万
+$31,491/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1320呎 (4+房)
+$3940万
+$29,846/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1316呎 (4+房)
+$3653万
+$27,755/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 1723呎 (4+房)
+$6802万
+$39,477/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 1160呎 (3房)
+$3540万
+$30,514/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1320呎 (4+房)
+$3928万
+$29,756/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1316呎 (4+房)
+$3642万
+$27,672/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 1723呎 (4+房)
+$5814万
+$33,745/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 1065呎 (3房)
+$3529万
+$33,136/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 1320呎 (4+房)
+$3837万
+$29,072/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 1316呎 (4+房)
+$3576万
+$27,174/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 1723呎 (4+房)
+$5815万
+$33,750/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 1160呎 (3房)
+$3501万
+$30,179/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 1320呎 (4+房)
+$3711万
+$28,112/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 1316呎 (4+房)
+$3512万
+$26,685/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 1723呎 (4+房)
+$5663万
+$32,869/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 1160呎 (3房)
+$3403万
+$29,337/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 1320呎 (4+房)
+$3477万
+$26,341/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 1221呎 (4+房)
+$3361万
+$27,524/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 1723呎 (4+房)
+$5448万
+$31,620/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 1065呎 (3房)
+$3308万
+$31,060/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 1320呎 (4+房)
+$3317万
+$25,130/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 1316呎 (4+房)
+$3139万
+$23,852/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 1723呎 (4+房)
+$5279万
+$30,640/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 1160呎 (3房)
+$3156万
+$27,204/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 1320呎 (4+房)
+$3085万
+$23,371/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 1316呎 (4+房)
+$2919万
+$22,182/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 1723呎 (4+房)
+$5534万
+$32,120/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 1065呎 (3房)
+$3045万
+$28,596/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 1320呎 (4+房)
+$3066万
+$23,230/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 1316呎 (4+房)
+$2902万
+$22,049/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 1723呎 (4+房)
+$4871万
+$28,272/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 1160呎 (3房)
+$2875万
+$24,784/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 1320呎 (4+房)
+$2529万
+$19,162/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 1221呎 (4+房)
+$2211万
+$18,105/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 1723呎 (4+房)
+$3896万
+$22,610/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 1160呎 (3房)
+$2329万
+$20,075/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 1150呎 (4+房)
+$3623万
+$31,505/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 1300呎 (4+房)
+$2506万
+$19,276/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 1723呎 (3房)
+$3909万
+$22,690/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 1143呎 (3房)
+$2173万
+$19,011/呎
+(16年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>3&amp;4</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 1929呎 (3房)
+$4593万
+$23,811/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 1970呎 (2房)
+$6277万
+$31,865/呎
+(16年-05月)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr"/>
+      <c r="E23" s="21" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-何文田-天铸 (第2期).xlsx
+++ b/files/九龙-何文田-天铸 (第2期).xlsx
@@ -647,7 +647,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -14112,10 +14112,35 @@
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 1428呎 (4+房)
+$4207万
+$29,461/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 1237呎 (3房)
+$3534万
+$28,573/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
           <t>22&amp;23</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 2199呎 (4+房)
 $11391万
@@ -14123,7 +14148,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 2361呎 (4+房)
 $12169万
@@ -14131,33 +14156,8 @@
 (16年-04月)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr"/>
-      <c r="C8" s="21" t="inlineStr"/>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>C | 1428呎 (4+房)
-$4207万
-$29,461/呎
-(16年-04月)</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>D | 1237呎 (3房)
-$3534万
-$28,573/呎
-(16年-04月)</t>
-        </is>
-      </c>
+      <c r="D8" s="21" t="inlineStr"/>
+      <c r="E8" s="21" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -14920,10 +14920,35 @@
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3250万
+$26,273/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$4251万
+$29,770/呎
+(16年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
           <t>22&amp;23</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 2265呎 (4+房)
 $15583万
@@ -14931,7 +14956,7 @@
 (19年-07月)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 2199呎 (4+房)
 $14260万
@@ -14939,33 +14964,8 @@
 (19年-02月)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr"/>
-      <c r="C8" s="21" t="inlineStr"/>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3250万
-$26,273/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$4251万
-$29,770/呎
-(16年-04月)</t>
-        </is>
-      </c>
+      <c r="D8" s="21" t="inlineStr"/>
+      <c r="E8" s="21" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">

--- a/files/九龙-何文田-天铸 (第2期).xlsx
+++ b/files/九龙-何文田-天铸 (第2期).xlsx
@@ -637,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J273"/>
+  <dimension ref="A1:N273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -650,6 +650,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -707,6 +711,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -753,6 +777,22 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>87189700</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>34834</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -803,6 +843,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -849,6 +909,22 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>102470000</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>41169</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -895,6 +971,22 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>130758500</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>53546</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -945,6 +1037,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -991,6 +1103,22 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>29773000</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>29953</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1037,6 +1165,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>34687400</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>30058</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1083,6 +1227,22 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>74784440</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>43203</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1129,6 +1289,22 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>77515500</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>40584</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1175,6 +1351,22 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>63960100</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>64346</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1221,6 +1413,22 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>63960100</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>55425</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1267,6 +1475,22 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>94663213</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>51927</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1313,6 +1537,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>84798000</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>44397</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1359,6 +1599,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>29684000</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>29863</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1405,6 +1661,22 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>33769500</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>29263</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1451,6 +1723,22 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>78540300</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>45373</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1497,6 +1785,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>72269000</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>37837</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1543,6 +1847,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>29507000</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>29685</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1589,6 +1909,22 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>33635000</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>29146</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1635,6 +1971,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>77538600</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>44794</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1681,6 +2033,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>86098888</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>45078</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1727,6 +2095,22 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>29418700</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>29596</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1773,6 +2157,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>33567900</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>29088</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1819,6 +2219,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>85293200</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>46787</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1865,6 +2281,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>85720000</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>44880</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1911,6 +2343,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>29330400</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>29507</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1957,6 +2405,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>33467200</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>29001</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2003,6 +2467,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>83331500</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>45711</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2049,6 +2529,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>76722000</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>40169</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2095,6 +2591,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>28949100</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>29124</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2141,6 +2653,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>32864700</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>28479</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2187,6 +2715,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>72952814</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>40018</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2233,6 +2777,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>80760000</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2279,6 +2839,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>28572800</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>28745</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2325,6 +2901,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>32108900</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>27824</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2371,6 +2963,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>69274000</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>38000</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2417,6 +3025,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>80866000</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>42338</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2463,6 +3087,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>27915600</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>28084</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2509,6 +3149,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>31370300</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>27184</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2555,6 +3211,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>151799500</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>83269</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2601,6 +3273,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>72074900</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>35698</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2647,6 +3335,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>27050200</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>27213</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2693,6 +3397,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>30084200</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>26069</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2739,6 +3459,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>50010500</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>27433</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2785,6 +3521,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>55883800</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>27679</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2831,6 +3583,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>26374000</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>26533</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2877,6 +3645,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>28579900</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>24766</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2923,6 +3707,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>50013700</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>27435</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2969,6 +3769,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>55880600</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>29257</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3015,6 +3831,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>25292600</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>25445</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3061,6 +3893,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>27408200</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>23751</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3107,6 +3955,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>42343700</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>23227</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3153,6 +4017,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>47026000</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>23292</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3199,6 +4079,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>20360500</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>20483</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3245,6 +4141,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>22885800</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>19832</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3291,6 +4203,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>63793000</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>34993</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3337,6 +4265,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>63793000</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>31596</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3383,6 +4327,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>18326000</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>21235</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3429,6 +4389,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>20703700</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>19812</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3475,6 +4451,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>30062200</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>16637</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3521,6 +4513,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>36130100</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>17895</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3567,6 +4575,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>54364100</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>23262</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3613,6 +4637,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>46739500</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>22634</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3659,6 +4699,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>77513800</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>37088</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3705,6 +4761,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>75094800</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>36121</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3751,6 +4823,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>148310000</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>55319</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3797,6 +4885,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>83483500</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>41206</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3843,6 +4947,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>35344900</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>28573</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3889,6 +5009,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>42070800</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>29461</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3935,6 +5071,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>121685400</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>51540</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3981,6 +5133,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>113910000</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>51801</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4027,6 +5195,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>35274400</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>28516</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4073,6 +5257,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>41944900</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>29373</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4119,6 +5319,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>71978700</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>44819</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4165,6 +5381,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>78199800</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>44994</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4211,6 +5443,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>35204000</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>28459</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4257,6 +5505,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>83513800</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>58483</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4303,6 +5567,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>74639600</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>46475</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4349,6 +5629,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>81825000</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>49711</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4395,6 +5691,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>35133700</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>28402</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4441,6 +5753,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>83513800</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>58483</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4487,6 +5815,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>69455700</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>40665</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4533,6 +5877,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>75834900</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>43633</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4579,6 +5939,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>35133700</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>28402</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4625,6 +6001,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>41694300</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>29198</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4671,6 +6063,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>70680000</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>44010</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4717,6 +6125,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>63980000</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>38870</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4763,6 +6187,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>34993800</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>28289</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4809,6 +6249,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>41445700</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>29024</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4855,6 +6311,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>67351700</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>39433</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4901,6 +6373,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>73177500</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>42104</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4947,6 +6435,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>34923900</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>28233</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4993,6 +6497,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>41321800</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>28937</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5039,6 +6559,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>66487300</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>38927</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5085,6 +6621,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>71883600</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>41360</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5131,6 +6683,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>34819200</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>30490</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5177,6 +6745,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>81448000</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>57036</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5223,6 +6807,22 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>68290000</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>42522</v>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5269,6 +6869,22 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>79109600</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>48062</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5315,6 +6931,22 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>34192400</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>29941</v>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5361,6 +6993,22 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>81448000</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>57036</v>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5407,6 +7055,22 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>64100400</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>37530</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5453,6 +7117,22 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>66524200</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>38276</v>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5499,6 +7179,22 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>33064000</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>26729</v>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5545,6 +7241,22 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>38922000</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>27256</v>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5591,6 +7303,22 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>59421100</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>34790</v>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5637,6 +7365,22 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>61668000</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>35482</v>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5683,6 +7427,22 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>31972900</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>25847</v>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5729,6 +7489,22 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>37637500</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>26357</v>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5775,6 +7551,22 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>49141200</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>28771</v>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5821,6 +7613,22 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>50804200</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>29231</v>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5867,6 +7675,22 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>31141600</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>25175</v>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5913,6 +7737,22 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>36659000</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>25672</v>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5959,6 +7799,22 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>41966500</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>24571</v>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6005,6 +7861,22 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>42878700</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>24671</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6051,6 +7923,22 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>30363100</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>24546</v>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6097,6 +7985,22 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>35925700</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>25158</v>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6143,6 +8047,22 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>40707600</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>23833</v>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6189,6 +8109,22 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>41592300</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>23931</v>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6235,6 +8171,22 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>28814600</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>23294</v>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6281,6 +8233,22 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>34093500</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>23875</v>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6327,6 +8295,22 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>39038600</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>22856</v>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6373,6 +8357,22 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>39887000</v>
+      </c>
+      <c r="L125" s="5" t="n">
+        <v>22950</v>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6419,6 +8419,22 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>23195700</v>
+      </c>
+      <c r="L126" s="5" t="n">
+        <v>18752</v>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6465,6 +8481,22 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>26172100</v>
+      </c>
+      <c r="L127" s="5" t="n">
+        <v>18328</v>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6511,6 +8543,22 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>29028400</v>
+      </c>
+      <c r="L128" s="5" t="n">
+        <v>16996</v>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6557,6 +8605,22 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>32064300</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>18449</v>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6603,6 +8667,22 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>21134800</v>
+      </c>
+      <c r="L130" s="5" t="n">
+        <v>17309</v>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6649,6 +8729,22 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>25970800</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>19615</v>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6695,6 +8791,22 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>29047100</v>
+      </c>
+      <c r="L132" s="5" t="n">
+        <v>17177</v>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6741,6 +8853,22 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>35028888</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>21490</v>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6787,6 +8915,22 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>76702500</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>35298</v>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6833,6 +8977,22 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>125400000</v>
+      </c>
+      <c r="L135" s="5" t="n">
+        <v>63015</v>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6879,6 +9039,22 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>152267800</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>56795</v>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6925,6 +9101,22 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>82484200</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>38761</v>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6971,6 +9163,22 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>42511300</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>29770</v>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7017,6 +9225,22 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="n">
+        <v>32500000</v>
+      </c>
+      <c r="L139" s="5" t="n">
+        <v>26273</v>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7063,6 +9287,22 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>142602800</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>64849</v>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7109,6 +9349,22 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>155826000</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>68797</v>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7155,6 +9411,22 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>42384100</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>29681</v>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7201,6 +9473,22 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>71332700</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>57666</v>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7247,6 +9535,22 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="5" t="n">
+        <v>66498900</v>
+      </c>
+      <c r="L144" s="5" t="n">
+        <v>38262</v>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7293,6 +9597,22 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>75670800</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>44304</v>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7339,6 +9659,22 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>42257300</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>29592</v>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7385,6 +9721,22 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>35559600</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>28747</v>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7431,6 +9783,22 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>65323000</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <v>37585</v>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7477,6 +9845,22 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>74718000</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>43746</v>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7523,6 +9907,22 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>42130900</v>
+      </c>
+      <c r="L150" s="5" t="n">
+        <v>29503</v>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7569,6 +9969,22 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>35488600</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>28689</v>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7615,6 +10031,22 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="n">
+        <v>64168100</v>
+      </c>
+      <c r="L152" s="5" t="n">
+        <v>36921</v>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7661,6 +10093,22 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="n">
+        <v>67636800</v>
+      </c>
+      <c r="L153" s="5" t="n">
+        <v>39600</v>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7707,6 +10155,22 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="n">
+        <v>42130900</v>
+      </c>
+      <c r="L154" s="5" t="n">
+        <v>29503</v>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7753,6 +10217,22 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="n">
+        <v>35488600</v>
+      </c>
+      <c r="L155" s="5" t="n">
+        <v>28689</v>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7799,6 +10279,22 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="n">
+        <v>134983100</v>
+      </c>
+      <c r="L156" s="5" t="n">
+        <v>77666</v>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7845,6 +10341,22 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>134983100</v>
+      </c>
+      <c r="L157" s="5" t="n">
+        <v>79030</v>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7891,6 +10403,22 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="n">
+        <v>41879700</v>
+      </c>
+      <c r="L158" s="5" t="n">
+        <v>29328</v>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7937,6 +10465,22 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="n">
+        <v>35347200</v>
+      </c>
+      <c r="L159" s="5" t="n">
+        <v>28575</v>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7983,6 +10527,22 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="n">
+        <v>61919400</v>
+      </c>
+      <c r="L160" s="5" t="n">
+        <v>35627</v>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8029,6 +10589,22 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="5" t="n">
+        <v>66622000</v>
+      </c>
+      <c r="L161" s="5" t="n">
+        <v>39006</v>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8075,6 +10651,22 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="n">
+        <v>41754400</v>
+      </c>
+      <c r="L162" s="5" t="n">
+        <v>29240</v>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8121,6 +10713,22 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>35276700</v>
+      </c>
+      <c r="L163" s="5" t="n">
+        <v>28518</v>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8167,6 +10775,22 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="n">
+        <v>60824600</v>
+      </c>
+      <c r="L164" s="5" t="n">
+        <v>34997</v>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8213,6 +10837,22 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>66628000</v>
+      </c>
+      <c r="L165" s="5" t="n">
+        <v>39009</v>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8259,6 +10899,22 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K166" s="5" t="n">
+        <v>41629100</v>
+      </c>
+      <c r="L166" s="5" t="n">
+        <v>29152</v>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8305,6 +10961,22 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="5" t="n">
+        <v>35170800</v>
+      </c>
+      <c r="L167" s="5" t="n">
+        <v>28432</v>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8351,6 +11023,22 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="5" t="n">
+        <v>60642100</v>
+      </c>
+      <c r="L168" s="5" t="n">
+        <v>34892</v>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8397,6 +11085,22 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="5" t="n">
+        <v>64830000</v>
+      </c>
+      <c r="L169" s="5" t="n">
+        <v>37957</v>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8443,6 +11147,22 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="5" t="n">
+        <v>40671700</v>
+      </c>
+      <c r="L170" s="5" t="n">
+        <v>28482</v>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N170" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8489,6 +11209,22 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="5" t="n">
+        <v>34537800</v>
+      </c>
+      <c r="L171" s="5" t="n">
+        <v>27921</v>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8535,6 +11271,22 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="5" t="n">
+        <v>58640900</v>
+      </c>
+      <c r="L172" s="5" t="n">
+        <v>33740</v>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N172" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8581,6 +11333,22 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="5" t="n">
+        <v>62900600</v>
+      </c>
+      <c r="L173" s="5" t="n">
+        <v>36827</v>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8627,6 +11395,22 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="5" t="n">
+        <v>39329500</v>
+      </c>
+      <c r="L174" s="5" t="n">
+        <v>27542</v>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8673,6 +11457,22 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="5" t="n">
+        <v>33398000</v>
+      </c>
+      <c r="L175" s="5" t="n">
+        <v>26999</v>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8719,6 +11519,22 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" s="5" t="n">
+        <v>54360100</v>
+      </c>
+      <c r="L176" s="5" t="n">
+        <v>31277</v>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N176" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8765,6 +11581,22 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="5" t="n">
+        <v>58896440</v>
+      </c>
+      <c r="L177" s="5" t="n">
+        <v>34483</v>
+      </c>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8811,6 +11643,22 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" s="5" t="n">
+        <v>38424900</v>
+      </c>
+      <c r="L178" s="5" t="n">
+        <v>26908</v>
+      </c>
+      <c r="M178" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N178" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8857,6 +11705,22 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="5" t="n">
+        <v>32629900</v>
+      </c>
+      <c r="L179" s="5" t="n">
+        <v>26378</v>
+      </c>
+      <c r="M179" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8903,6 +11767,22 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K180" s="5" t="n">
+        <v>44412200</v>
+      </c>
+      <c r="L180" s="5" t="n">
+        <v>25554</v>
+      </c>
+      <c r="M180" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N180" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8949,6 +11829,22 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="5" t="n">
+        <v>55668000</v>
+      </c>
+      <c r="L181" s="5" t="n">
+        <v>32593</v>
+      </c>
+      <c r="M181" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8995,6 +11891,22 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="5" t="n">
+        <v>37425800</v>
+      </c>
+      <c r="L182" s="5" t="n">
+        <v>26209</v>
+      </c>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N182" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9041,6 +11953,22 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="5" t="n">
+        <v>31781500</v>
+      </c>
+      <c r="L183" s="5" t="n">
+        <v>25692</v>
+      </c>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9087,6 +12015,22 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K184" s="5" t="n">
+        <v>80627200</v>
+      </c>
+      <c r="L184" s="5" t="n">
+        <v>46391</v>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N184" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9133,6 +12077,22 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K185" s="5" t="n">
+        <v>80627200</v>
+      </c>
+      <c r="L185" s="5" t="n">
+        <v>47206</v>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N185" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9179,6 +12139,22 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K186" s="5" t="n">
+        <v>36303100</v>
+      </c>
+      <c r="L186" s="5" t="n">
+        <v>25422</v>
+      </c>
+      <c r="M186" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N186" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9225,6 +12201,22 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K187" s="5" t="n">
+        <v>31145900</v>
+      </c>
+      <c r="L187" s="5" t="n">
+        <v>25179</v>
+      </c>
+      <c r="M187" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N187" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9271,6 +12263,22 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K188" s="5" t="n">
+        <v>38910400</v>
+      </c>
+      <c r="L188" s="5" t="n">
+        <v>22388</v>
+      </c>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N188" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9317,6 +12325,22 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K189" s="5" t="n">
+        <v>53323000</v>
+      </c>
+      <c r="L189" s="5" t="n">
+        <v>31220</v>
+      </c>
+      <c r="M189" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N189" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9363,6 +12387,22 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K190" s="5" t="n">
+        <v>32273500</v>
+      </c>
+      <c r="L190" s="5" t="n">
+        <v>22600</v>
+      </c>
+      <c r="M190" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N190" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9409,6 +12449,22 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K191" s="5" t="n">
+        <v>28000100</v>
+      </c>
+      <c r="L191" s="5" t="n">
+        <v>22635</v>
+      </c>
+      <c r="M191" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N191" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9455,6 +12511,22 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K192" s="5" t="n">
+        <v>37898700</v>
+      </c>
+      <c r="L192" s="5" t="n">
+        <v>21806</v>
+      </c>
+      <c r="M192" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N192" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9501,6 +12573,22 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K193" s="5" t="n">
+        <v>51885000</v>
+      </c>
+      <c r="L193" s="5" t="n">
+        <v>30378</v>
+      </c>
+      <c r="M193" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N193" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9547,6 +12635,22 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K194" s="5" t="n">
+        <v>24990300</v>
+      </c>
+      <c r="L194" s="5" t="n">
+        <v>17500</v>
+      </c>
+      <c r="M194" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N194" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9593,6 +12697,22 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K195" s="5" t="n">
+        <v>20820400</v>
+      </c>
+      <c r="L195" s="5" t="n">
+        <v>16831</v>
+      </c>
+      <c r="M195" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N195" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9639,6 +12759,22 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K196" s="5" t="n">
+        <v>31266400</v>
+      </c>
+      <c r="L196" s="5" t="n">
+        <v>17990</v>
+      </c>
+      <c r="M196" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N196" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9685,6 +12821,22 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K197" s="5" t="n">
+        <v>50488888</v>
+      </c>
+      <c r="L197" s="5" t="n">
+        <v>29560</v>
+      </c>
+      <c r="M197" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N197" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9731,6 +12883,22 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K198" s="5" t="n">
+        <v>24209100</v>
+      </c>
+      <c r="L198" s="5" t="n">
+        <v>17145</v>
+      </c>
+      <c r="M198" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N198" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9777,6 +12945,22 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K199" s="5" t="n">
+        <v>21984300</v>
+      </c>
+      <c r="L199" s="5" t="n">
+        <v>18005</v>
+      </c>
+      <c r="M199" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N199" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9823,6 +13007,22 @@
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K200" s="5" t="n">
+        <v>30613100</v>
+      </c>
+      <c r="L200" s="5" t="n">
+        <v>17778</v>
+      </c>
+      <c r="M200" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N200" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9869,6 +13069,22 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K201" s="5" t="n">
+        <v>31662800</v>
+      </c>
+      <c r="L201" s="5" t="n">
+        <v>18724</v>
+      </c>
+      <c r="M201" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N201" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9915,6 +13131,22 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K202" s="5" t="n">
+        <v>151799500</v>
+      </c>
+      <c r="L202" s="5" t="n">
+        <v>69410</v>
+      </c>
+      <c r="M202" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N202" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9961,6 +13193,22 @@
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K203" s="5" t="n">
+        <v>91650000</v>
+      </c>
+      <c r="L203" s="5" t="n">
+        <v>43028</v>
+      </c>
+      <c r="M203" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N203" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10007,6 +13255,22 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" s="5" t="n">
+        <v>213912000</v>
+      </c>
+      <c r="L204" s="5" t="n">
+        <v>78270</v>
+      </c>
+      <c r="M204" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N204" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10053,6 +13317,22 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" s="5" t="n">
+        <v>128601000</v>
+      </c>
+      <c r="L205" s="5" t="n">
+        <v>62916</v>
+      </c>
+      <c r="M205" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N205" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10099,6 +13379,22 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" s="5" t="n">
+        <v>39981600</v>
+      </c>
+      <c r="L206" s="5" t="n">
+        <v>30381</v>
+      </c>
+      <c r="M206" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N206" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10145,6 +13441,22 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" s="5" t="n">
+        <v>43077300</v>
+      </c>
+      <c r="L207" s="5" t="n">
+        <v>32634</v>
+      </c>
+      <c r="M207" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N207" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10191,6 +13503,22 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" s="5" t="n">
+        <v>38618900</v>
+      </c>
+      <c r="L208" s="5" t="n">
+        <v>33292</v>
+      </c>
+      <c r="M208" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N208" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10237,6 +13565,22 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K209" s="5" t="n">
+        <v>70738800</v>
+      </c>
+      <c r="L209" s="5" t="n">
+        <v>41056</v>
+      </c>
+      <c r="M209" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N209" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10283,6 +13627,22 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K210" s="5" t="n">
+        <v>39468600</v>
+      </c>
+      <c r="L210" s="5" t="n">
+        <v>32325</v>
+      </c>
+      <c r="M210" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N210" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10329,6 +13689,22 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" s="5" t="n">
+        <v>42946400</v>
+      </c>
+      <c r="L211" s="5" t="n">
+        <v>32535</v>
+      </c>
+      <c r="M211" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N211" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10375,6 +13751,22 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" s="5" t="n">
+        <v>38407700</v>
+      </c>
+      <c r="L212" s="5" t="n">
+        <v>33110</v>
+      </c>
+      <c r="M212" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N212" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10421,6 +13813,22 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K213" s="5" t="n">
+        <v>71444000</v>
+      </c>
+      <c r="L213" s="5" t="n">
+        <v>41465</v>
+      </c>
+      <c r="M213" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N213" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10467,6 +13875,22 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" s="5" t="n">
+        <v>38962000</v>
+      </c>
+      <c r="L214" s="5" t="n">
+        <v>31910</v>
+      </c>
+      <c r="M214" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N214" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10513,6 +13937,22 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" s="5" t="n">
+        <v>42732700</v>
+      </c>
+      <c r="L215" s="5" t="n">
+        <v>32373</v>
+      </c>
+      <c r="M215" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N215" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10559,6 +13999,22 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K216" s="5" t="n">
+        <v>38197600</v>
+      </c>
+      <c r="L216" s="5" t="n">
+        <v>32929</v>
+      </c>
+      <c r="M216" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N216" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10605,6 +14061,22 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" s="5" t="n">
+        <v>63585000</v>
+      </c>
+      <c r="L217" s="5" t="n">
+        <v>36904</v>
+      </c>
+      <c r="M217" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N217" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10651,6 +14123,22 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" s="5" t="n">
+        <v>76431800</v>
+      </c>
+      <c r="L218" s="5" t="n">
+        <v>58079</v>
+      </c>
+      <c r="M218" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N218" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10697,6 +14185,22 @@
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" s="5" t="n">
+        <v>41895500</v>
+      </c>
+      <c r="L219" s="5" t="n">
+        <v>31739</v>
+      </c>
+      <c r="M219" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N219" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10743,6 +14247,22 @@
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" s="5" t="n">
+        <v>76431800</v>
+      </c>
+      <c r="L220" s="5" t="n">
+        <v>65889</v>
+      </c>
+      <c r="M220" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N220" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10789,6 +14309,22 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" s="5" t="n">
+        <v>53423338</v>
+      </c>
+      <c r="L221" s="5" t="n">
+        <v>31006</v>
+      </c>
+      <c r="M221" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N221" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10835,6 +14371,22 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" s="5" t="n">
+        <v>37968500</v>
+      </c>
+      <c r="L222" s="5" t="n">
+        <v>28851</v>
+      </c>
+      <c r="M222" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N222" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10881,6 +14433,22 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" s="5" t="n">
+        <v>41964900</v>
+      </c>
+      <c r="L223" s="5" t="n">
+        <v>31792</v>
+      </c>
+      <c r="M223" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N223" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10927,6 +14495,22 @@
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K224" s="5" t="n">
+        <v>37816800</v>
+      </c>
+      <c r="L224" s="5" t="n">
+        <v>32601</v>
+      </c>
+      <c r="M224" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N224" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10973,6 +14557,22 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K225" s="5" t="n">
+        <v>62677000</v>
+      </c>
+      <c r="L225" s="5" t="n">
+        <v>36377</v>
+      </c>
+      <c r="M225" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N225" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11019,6 +14619,22 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K226" s="5" t="n">
+        <v>37592500</v>
+      </c>
+      <c r="L226" s="5" t="n">
+        <v>28566</v>
+      </c>
+      <c r="M226" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N226" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11065,6 +14681,22 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K227" s="5" t="n">
+        <v>41549400</v>
+      </c>
+      <c r="L227" s="5" t="n">
+        <v>31477</v>
+      </c>
+      <c r="M227" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N227" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11111,6 +14743,22 @@
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K228" s="5" t="n">
+        <v>36529200</v>
+      </c>
+      <c r="L228" s="5" t="n">
+        <v>31491</v>
+      </c>
+      <c r="M228" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N228" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11157,6 +14805,22 @@
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K229" s="5" t="n">
+        <v>64512640</v>
+      </c>
+      <c r="L229" s="5" t="n">
+        <v>37442</v>
+      </c>
+      <c r="M229" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N229" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11203,6 +14867,22 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K230" s="5" t="n">
+        <v>37000500</v>
+      </c>
+      <c r="L230" s="5" t="n">
+        <v>30303</v>
+      </c>
+      <c r="M230" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N230" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11249,6 +14929,22 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K231" s="5" t="n">
+        <v>40105600</v>
+      </c>
+      <c r="L231" s="5" t="n">
+        <v>30383</v>
+      </c>
+      <c r="M231" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N231" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11295,6 +14991,22 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" s="5" t="n">
+        <v>35396400</v>
+      </c>
+      <c r="L232" s="5" t="n">
+        <v>30514</v>
+      </c>
+      <c r="M232" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N232" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11341,6 +15053,22 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K233" s="5" t="n">
+        <v>68018820</v>
+      </c>
+      <c r="L233" s="5" t="n">
+        <v>39477</v>
+      </c>
+      <c r="M233" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N233" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11387,6 +15115,22 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K234" s="5" t="n">
+        <v>36525700</v>
+      </c>
+      <c r="L234" s="5" t="n">
+        <v>27755</v>
+      </c>
+      <c r="M234" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N234" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11433,6 +15177,22 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K235" s="5" t="n">
+        <v>39396400</v>
+      </c>
+      <c r="L235" s="5" t="n">
+        <v>29846</v>
+      </c>
+      <c r="M235" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N235" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11479,6 +15239,22 @@
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K236" s="5" t="n">
+        <v>35290300</v>
+      </c>
+      <c r="L236" s="5" t="n">
+        <v>33136</v>
+      </c>
+      <c r="M236" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N236" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11525,6 +15301,22 @@
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K237" s="5" t="n">
+        <v>58143200</v>
+      </c>
+      <c r="L237" s="5" t="n">
+        <v>33745</v>
+      </c>
+      <c r="M237" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N237" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11571,6 +15363,22 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K238" s="5" t="n">
+        <v>36416100</v>
+      </c>
+      <c r="L238" s="5" t="n">
+        <v>27672</v>
+      </c>
+      <c r="M238" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N238" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11617,6 +15425,22 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K239" s="5" t="n">
+        <v>39278300</v>
+      </c>
+      <c r="L239" s="5" t="n">
+        <v>29756</v>
+      </c>
+      <c r="M239" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N239" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11663,6 +15487,22 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K240" s="5" t="n">
+        <v>35007900</v>
+      </c>
+      <c r="L240" s="5" t="n">
+        <v>30179</v>
+      </c>
+      <c r="M240" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N240" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11709,6 +15549,22 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K241" s="5" t="n">
+        <v>58150600</v>
+      </c>
+      <c r="L241" s="5" t="n">
+        <v>33750</v>
+      </c>
+      <c r="M241" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N241" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11755,6 +15611,22 @@
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K242" s="5" t="n">
+        <v>35760600</v>
+      </c>
+      <c r="L242" s="5" t="n">
+        <v>27174</v>
+      </c>
+      <c r="M242" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N242" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11801,6 +15673,22 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K243" s="5" t="n">
+        <v>38374900</v>
+      </c>
+      <c r="L243" s="5" t="n">
+        <v>29072</v>
+      </c>
+      <c r="M243" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N243" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11847,6 +15735,22 @@
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K244" s="5" t="n">
+        <v>34031200</v>
+      </c>
+      <c r="L244" s="5" t="n">
+        <v>29337</v>
+      </c>
+      <c r="M244" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N244" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11893,6 +15797,22 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K245" s="5" t="n">
+        <v>56633900</v>
+      </c>
+      <c r="L245" s="5" t="n">
+        <v>32869</v>
+      </c>
+      <c r="M245" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N245" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11939,6 +15859,22 @@
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K246" s="5" t="n">
+        <v>35117000</v>
+      </c>
+      <c r="L246" s="5" t="n">
+        <v>26685</v>
+      </c>
+      <c r="M246" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N246" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11985,6 +15921,22 @@
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K247" s="5" t="n">
+        <v>37108500</v>
+      </c>
+      <c r="L247" s="5" t="n">
+        <v>28112</v>
+      </c>
+      <c r="M247" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N247" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12031,6 +15983,22 @@
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K248" s="5" t="n">
+        <v>33078400</v>
+      </c>
+      <c r="L248" s="5" t="n">
+        <v>31060</v>
+      </c>
+      <c r="M248" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N248" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12077,6 +16045,22 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K249" s="5" t="n">
+        <v>54481700</v>
+      </c>
+      <c r="L249" s="5" t="n">
+        <v>31620</v>
+      </c>
+      <c r="M249" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N249" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12123,6 +16107,22 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K250" s="5" t="n">
+        <v>33606900</v>
+      </c>
+      <c r="L250" s="5" t="n">
+        <v>27524</v>
+      </c>
+      <c r="M250" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N250" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12169,6 +16169,22 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K251" s="5" t="n">
+        <v>34770700</v>
+      </c>
+      <c r="L251" s="5" t="n">
+        <v>26341</v>
+      </c>
+      <c r="M251" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N251" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12215,6 +16231,22 @@
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K252" s="5" t="n">
+        <v>31556800</v>
+      </c>
+      <c r="L252" s="5" t="n">
+        <v>27204</v>
+      </c>
+      <c r="M252" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N252" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12261,6 +16293,22 @@
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K253" s="5" t="n">
+        <v>52792900</v>
+      </c>
+      <c r="L253" s="5" t="n">
+        <v>30640</v>
+      </c>
+      <c r="M253" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N253" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12307,6 +16355,22 @@
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K254" s="5" t="n">
+        <v>31388900</v>
+      </c>
+      <c r="L254" s="5" t="n">
+        <v>23852</v>
+      </c>
+      <c r="M254" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N254" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12353,6 +16417,22 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K255" s="5" t="n">
+        <v>33171200</v>
+      </c>
+      <c r="L255" s="5" t="n">
+        <v>25130</v>
+      </c>
+      <c r="M255" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N255" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12399,6 +16479,22 @@
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K256" s="5" t="n">
+        <v>30454700</v>
+      </c>
+      <c r="L256" s="5" t="n">
+        <v>28596</v>
+      </c>
+      <c r="M256" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N256" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12445,6 +16541,22 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K257" s="5" t="n">
+        <v>55342040</v>
+      </c>
+      <c r="L257" s="5" t="n">
+        <v>32120</v>
+      </c>
+      <c r="M257" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N257" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12491,6 +16603,22 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K258" s="5" t="n">
+        <v>29191600</v>
+      </c>
+      <c r="L258" s="5" t="n">
+        <v>22182</v>
+      </c>
+      <c r="M258" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N258" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12537,6 +16665,22 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K259" s="5" t="n">
+        <v>30849200</v>
+      </c>
+      <c r="L259" s="5" t="n">
+        <v>23371</v>
+      </c>
+      <c r="M259" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N259" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12583,6 +16727,22 @@
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K260" s="5" t="n">
+        <v>28749300</v>
+      </c>
+      <c r="L260" s="5" t="n">
+        <v>24784</v>
+      </c>
+      <c r="M260" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N260" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12629,6 +16789,22 @@
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K261" s="5" t="n">
+        <v>48712000</v>
+      </c>
+      <c r="L261" s="5" t="n">
+        <v>28272</v>
+      </c>
+      <c r="M261" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N261" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12675,6 +16851,22 @@
       </c>
       <c r="J262" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K262" s="5" t="n">
+        <v>29016400</v>
+      </c>
+      <c r="L262" s="5" t="n">
+        <v>22049</v>
+      </c>
+      <c r="M262" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N262" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12721,6 +16913,22 @@
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K263" s="5" t="n">
+        <v>30664100</v>
+      </c>
+      <c r="L263" s="5" t="n">
+        <v>23230</v>
+      </c>
+      <c r="M263" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N263" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12767,6 +16975,22 @@
       </c>
       <c r="J264" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" s="5" t="n">
+        <v>23286900</v>
+      </c>
+      <c r="L264" s="5" t="n">
+        <v>20075</v>
+      </c>
+      <c r="M264" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N264" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12813,6 +17037,22 @@
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K265" s="5" t="n">
+        <v>38956200</v>
+      </c>
+      <c r="L265" s="5" t="n">
+        <v>22610</v>
+      </c>
+      <c r="M265" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N265" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12859,6 +17099,22 @@
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K266" s="5" t="n">
+        <v>22105600</v>
+      </c>
+      <c r="L266" s="5" t="n">
+        <v>18105</v>
+      </c>
+      <c r="M266" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N266" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12905,6 +17161,22 @@
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K267" s="5" t="n">
+        <v>25293900</v>
+      </c>
+      <c r="L267" s="5" t="n">
+        <v>19162</v>
+      </c>
+      <c r="M267" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N267" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12951,6 +17223,22 @@
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K268" s="5" t="n">
+        <v>21729500</v>
+      </c>
+      <c r="L268" s="5" t="n">
+        <v>19011</v>
+      </c>
+      <c r="M268" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N268" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12997,6 +17285,22 @@
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K269" s="5" t="n">
+        <v>39094700</v>
+      </c>
+      <c r="L269" s="5" t="n">
+        <v>22690</v>
+      </c>
+      <c r="M269" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N269" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13043,6 +17347,22 @@
       </c>
       <c r="J270" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K270" s="5" t="n">
+        <v>25059000</v>
+      </c>
+      <c r="L270" s="5" t="n">
+        <v>19276</v>
+      </c>
+      <c r="M270" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N270" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13089,6 +17409,22 @@
       </c>
       <c r="J271" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K271" s="5" t="n">
+        <v>36231000</v>
+      </c>
+      <c r="L271" s="5" t="n">
+        <v>31505</v>
+      </c>
+      <c r="M271" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N271" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13135,6 +17471,22 @@
       </c>
       <c r="J272" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K272" s="5" t="n">
+        <v>62774600</v>
+      </c>
+      <c r="L272" s="5" t="n">
+        <v>31865</v>
+      </c>
+      <c r="M272" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N272" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13181,13 +17533,29 @@
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K273" s="5" t="n">
+        <v>45931400</v>
+      </c>
+      <c r="L273" s="5" t="n">
+        <v>23811</v>
+      </c>
+      <c r="M273" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N273" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -13328,7 +17696,7 @@
           <t>C | 2503呎 (4+房)
 $8719万
 $34,834/呎
-(16年-04月)</t>
+(16年-04月-07日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr"/>
@@ -13352,7 +17720,7 @@
           <t>B | 2442呎 (4+房)
 $13076万
 $53,546/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -13360,7 +17728,7 @@
           <t>C | 2489呎 (4+房)
 $10247万
 $41,169/呎
-(16年-04月)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr"/>
@@ -13376,7 +17744,7 @@
           <t>A | 1910呎 (4+房)
 $7752万
 $40,584/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -13384,7 +17752,7 @@
           <t>B | 1731呎 (4+房)
 $7478万
 $43,203/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -13392,7 +17760,7 @@
           <t>C | 1154呎 (3房)
 $3469万
 $30,058/呎
-(16年-05月)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -13400,7 +17768,7 @@
           <t>D | 994呎 (3房)
 $2977万
 $29,953/呎
-(16年-05月)</t>
+(16年-05月-08日)</t>
         </is>
       </c>
     </row>
@@ -13415,7 +17783,7 @@
           <t>A | 1910呎 (4+房)
 $8480万
 $44,397/呎
-(19年-04月)</t>
+(19年-04月-03日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -13423,7 +17791,7 @@
           <t>B | 1823呎 (4+房)
 $9466万
 $51,927/呎
-(16年-05月)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -13431,7 +17799,7 @@
           <t>C | 1154呎 (3房)
 $6396万
 $55,425/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -13439,7 +17807,7 @@
           <t>D | 994呎 (3房)
 $6396万
 $64,346/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -13454,7 +17822,7 @@
           <t>A | 1910呎 (4+房)
 $7227万
 $37,837/呎
-(25年-08月)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -13462,7 +17830,7 @@
           <t>B | 1731呎 (4+房)
 $7854万
 $45,373/呎
-(23年-03月)</t>
+(23年-03月-20日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -13470,7 +17838,7 @@
           <t>C | 1154呎 (3房)
 $3377万
 $29,263/呎
-(16年-04月)</t>
+(16年-04月-07日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -13478,7 +17846,7 @@
           <t>D | 994呎 (3房)
 $2968万
 $29,863/呎
-(16年-05月)</t>
+(16年-05月-05日)</t>
         </is>
       </c>
     </row>
@@ -13493,7 +17861,7 @@
           <t>A | 1910呎 (4+房)
 $8610万
 $45,078/呎
-(23年-03月)</t>
+(23年-03月-05日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -13501,7 +17869,7 @@
           <t>B | 1731呎 (4+房)
 $7754万
 $44,794/呎
-(23年-04月)</t>
+(23年-04月-03日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -13509,7 +17877,7 @@
           <t>C | 1154呎 (3房)
 $3364万
 $29,146/呎
-(16年-04月)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -13517,7 +17885,7 @@
           <t>D | 994呎 (3房)
 $2951万
 $29,685/呎
-(16年-05月)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -13532,7 +17900,7 @@
           <t>A | 1910呎 (4+房)
 $8572万
 $44,880/呎
-(23年-03月)</t>
+(23年-03月-02日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -13540,7 +17908,7 @@
           <t>B | 1823呎 (4+房)
 $8529万
 $46,787/呎
-(16年-05月)</t>
+(16年-05月-08日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -13548,7 +17916,7 @@
           <t>C | 1154呎 (3房)
 $3357万
 $29,088/呎
-(16年-05月)</t>
+(16年-05月-15日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -13556,7 +17924,7 @@
           <t>D | 994呎 (3房)
 $2942万
 $29,596/呎
-(16年-05月)</t>
+(16年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -13571,7 +17939,7 @@
           <t>A | 1910呎 (4+房)
 $7672万
 $40,169/呎
-(19年-04月)</t>
+(19年-04月-03日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -13579,7 +17947,7 @@
           <t>B | 1823呎 (4+房)
 $8333万
 $45,711/呎
-(16年-05月)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -13587,7 +17955,7 @@
           <t>C | 1154呎 (3房)
 $3347万
 $29,001/呎
-(16年-05月)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -13595,7 +17963,7 @@
           <t>D | 994呎 (3房)
 $2933万
 $29,507/呎
-(16年-05月)</t>
+(16年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -13610,7 +17978,7 @@
           <t>A | 2019呎 (4+房)
 $8076万
 $40,000/呎
-(19年-09月)</t>
+(19年-09月-22日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -13618,7 +17986,7 @@
           <t>B | 1823呎 (4+房)
 $7295万
 $40,018/呎
-(21年-11月)</t>
+(21年-11月-16日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -13626,7 +17994,7 @@
           <t>C | 1154呎 (3房)
 $3286万
 $28,479/呎
-(16年-05月)</t>
+(16年-05月-02日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -13634,7 +18002,7 @@
           <t>D | 994呎 (3房)
 $2895万
 $29,124/呎
-(16年-05月)</t>
+(16年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -13649,7 +18017,7 @@
           <t>A | 1910呎 (4+房)
 $8087万
 $42,338/呎
-(19年-04月)</t>
+(19年-04月-09日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -13657,7 +18025,7 @@
           <t>B | 1823呎 (4+房)
 $6927万
 $38,000/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -13665,7 +18033,7 @@
           <t>C | 1154呎 (3房)
 $3211万
 $27,824/呎
-(16年-05月)</t>
+(16年-05月-02日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -13673,7 +18041,7 @@
           <t>D | 994呎 (3房)
 $2857万
 $28,745/呎
-(16年-05月)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -13688,7 +18056,7 @@
           <t>A | 2019呎 (4+房)
 $7207万
 $35,698/呎
-(16年-05月)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -13696,7 +18064,7 @@
           <t>B | 1823呎 (4+房)
 $15180万
 $83,269/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -13704,7 +18072,7 @@
           <t>C | 1154呎 (3房)
 $3137万
 $27,184/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -13712,7 +18080,7 @@
           <t>D | 994呎 (3房)
 $2792万
 $28,084/呎
-(16年-05月)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -13727,7 +18095,7 @@
           <t>A | 2019呎 (4+房)
 $5588万
 $27,679/呎
-(16年-04月)</t>
+(16年-04月-25日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -13735,7 +18103,7 @@
           <t>B | 1823呎 (4+房)
 $5001万
 $27,433/呎
-(16年-05月)</t>
+(16年-05月-04日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -13743,7 +18111,7 @@
           <t>C | 1154呎 (3房)
 $3008万
 $26,069/呎
-(16年-04月)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -13751,7 +18119,7 @@
           <t>D | 994呎 (3房)
 $2705万
 $27,213/呎
-(16年-05月)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -13766,7 +18134,7 @@
           <t>A | 1910呎 (4+房)
 $5588万
 $29,257/呎
-(16年-05月)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -13774,7 +18142,7 @@
           <t>B | 1823呎 (4+房)
 $5001万
 $27,435/呎
-(16年-05月)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -13782,7 +18150,7 @@
           <t>C | 1154呎 (3房)
 $2858万
 $24,766/呎
-(16年-05月)</t>
+(16年-05月-05日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -13790,7 +18158,7 @@
           <t>D | 994呎 (3房)
 $2637万
 $26,533/呎
-(16年-05月)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -13805,7 +18173,7 @@
           <t>A | 2019呎 (4+房)
 $4703万
 $23,292/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -13813,7 +18181,7 @@
           <t>B | 1823呎 (4+房)
 $4234万
 $23,227/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -13821,7 +18189,7 @@
           <t>C | 1154呎 (3房)
 $2741万
 $23,751/呎
-(16年-04月)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -13829,7 +18197,7 @@
           <t>D | 994呎 (3房)
 $2529万
 $25,445/呎
-(16年-05月)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -13844,7 +18212,7 @@
           <t>A | 2019呎 (4+房)
 $6379万
 $31,596/呎
-(16年-03月)</t>
+(16年-03月-31日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -13852,7 +18220,7 @@
           <t>B | 1823呎 (4+房)
 $6379万
 $34,993/呎
-(16年-03月)</t>
+(16年-03月-31日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -13860,7 +18228,7 @@
           <t>C | 1154呎 (3房)
 $2289万
 $19,832/呎
-(16年-05月)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -13868,7 +18236,7 @@
           <t>D | 994呎 (3房)
 $2036万
 $20,483/呎
-(16年-05月)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -13883,7 +18251,7 @@
           <t>A | 2019呎 (4+房)
 $3613万
 $17,895/呎
-(16年-04月)</t>
+(16年-04月-18日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -13891,7 +18259,7 @@
           <t>B | 1807呎 (4+房)
 $3006万
 $16,637/呎
-(16年-05月)</t>
+(16年-05月-08日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -13899,7 +18267,7 @@
           <t>C | 1045呎 (3房)
 $2070万
 $19,812/呎
-(16年-04月)</t>
+(16年-04月-24日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -13907,7 +18275,7 @@
           <t>D | 863呎 (3房)
 $1833万
 $21,235/呎
-(16年-05月)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -13922,7 +18290,7 @@
           <t>A | 2065呎 (3房)
 $4674万
 $22,634/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -13930,7 +18298,7 @@
           <t>B | 2337呎 (4+房)
 $5436万
 $23,262/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr"/>
@@ -14070,7 +18438,7 @@
           <t>A | 2681呎 (4+房)
 $14831万
 $55,319/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -14079,7 +18447,7 @@
           <t>C | 2079呎 (3房)
 $7509万
 $36,121/呎
-(16年-04月)</t>
+(16年-04月-25日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -14087,7 +18455,7 @@
           <t>D | 2090呎 (3房)
 $7751万
 $37,088/呎
-(16年-05月)</t>
+(16年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -14104,7 +18472,7 @@
           <t>C | 2026呎 (4+房)
 $8348万
 $41,206/呎
-(16年-05月)</t>
+(16年-05月-10日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr"/>
@@ -14112,52 +18480,52 @@
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
+          <t>22&amp;23</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 2199呎 (4+房)
+$11391万
+$51,801/呎
+(24年-04月-28日)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 2361呎 (4+房)
+$12169万
+$51,540/呎
+(16年-04月-21日)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr"/>
+      <c r="C8" s="21" t="inlineStr"/>
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 1428呎 (4+房)
 $4207万
 $29,461/呎
-(16年-04月)</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr">
+(16年-04月-19日)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 1237呎 (3房)
 $3534万
 $28,573/呎
-(16年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>22&amp;23</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>A | 2199呎 (4+房)
-$11391万
-$51,801/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>B | 2361呎 (4+房)
-$12169万
-$51,540/呎
-(16年-04月)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr"/>
-      <c r="E8" s="21" t="inlineStr"/>
+(16年-04月-19日)</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -14170,7 +18538,7 @@
           <t>A | 1738呎 (4+房)
 $7820万
 $44,994/呎
-(16年-05月)</t>
+(16年-05月-05日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -14178,7 +18546,7 @@
           <t>B | 1606呎 (4+房)
 $7198万
 $44,819/呎
-(16年-04月)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -14186,7 +18554,7 @@
           <t>C | 1428呎 (4+房)
 $4194万
 $29,373/呎
-(16年-04月)</t>
+(16年-04月-17日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -14194,7 +18562,7 @@
           <t>D | 1237呎 (3房)
 $3527万
 $28,516/呎
-(16年-04月)</t>
+(16年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -14209,7 +18577,7 @@
           <t>A | 1646呎 (4+房)
 $8182万
 $49,711/呎
-(19年-01月)</t>
+(19年-01月-27日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -14217,7 +18585,7 @@
           <t>B | 1606呎 (4+房)
 $7464万
 $46,475/呎
-(19年-03月)</t>
+(19年-03月-03日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -14225,7 +18593,7 @@
           <t>C | 1428呎 (4+房)
 $8351万
 $58,483/呎
-(16年-03月)</t>
+(16年-03月-24日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -14233,7 +18601,7 @@
           <t>D | 1237呎 (3房)
 $3520万
 $28,459/呎
-(16年-04月)</t>
+(16年-04月-12日)</t>
         </is>
       </c>
     </row>
@@ -14248,7 +18616,7 @@
           <t>A | 1738呎 (4+房)
 $7583万
 $43,633/呎
-(16年-04月)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -14256,7 +18624,7 @@
           <t>B | 1708呎 (4+房)
 $6946万
 $40,665/呎
-(16年-05月)</t>
+(16年-05月-08日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -14264,7 +18632,7 @@
           <t>C | 1428呎 (4+房)
 $8351万
 $58,483/呎
-(16年-03月)</t>
+(16年-03月-24日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -14272,7 +18640,7 @@
           <t>D | 1237呎 (3房)
 $3513万
 $28,402/呎
-(16年-04月)</t>
+(16年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -14287,7 +18655,7 @@
           <t>A | 1646呎 (4+房)
 $6398万
 $38,870/呎
-(24年-10月)</t>
+(24年-10月-14日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -14295,7 +18663,7 @@
           <t>B | 1606呎 (4+房)
 $7068万
 $44,010/呎
-(26年-01月)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -14303,7 +18671,7 @@
           <t>C | 1428呎 (4+房)
 $4169万
 $29,198/呎
-(16年-04月)</t>
+(16年-04月-17日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -14311,7 +18679,7 @@
           <t>D | 1237呎 (3房)
 $3513万
 $28,402/呎
-(16年-04月)</t>
+(16年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -14326,7 +18694,7 @@
           <t>A | 1738呎 (4+房)
 $7318万
 $42,104/呎
-(16年-04月)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -14334,7 +18702,7 @@
           <t>B | 1708呎 (4+房)
 $6735万
 $39,433/呎
-(16年-05月)</t>
+(16年-05月-11日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -14342,7 +18710,7 @@
           <t>C | 1428呎 (4+房)
 $4145万
 $29,024/呎
-(16年-04月)</t>
+(16年-04月-17日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -14350,7 +18718,7 @@
           <t>D | 1237呎 (3房)
 $3499万
 $28,289/呎
-(16年-04月)</t>
+(16年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -14365,7 +18733,7 @@
           <t>A | 1738呎 (4+房)
 $7188万
 $41,360/呎
-(16年-04月)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -14373,7 +18741,7 @@
           <t>B | 1708呎 (4+房)
 $6649万
 $38,927/呎
-(16年-04月)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -14381,7 +18749,7 @@
           <t>C | 1428呎 (4+房)
 $4132万
 $28,937/呎
-(16年-04月)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -14389,7 +18757,7 @@
           <t>D | 1237呎 (3房)
 $3492万
 $28,233/呎
-(16年-04月)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
     </row>
@@ -14404,7 +18772,7 @@
           <t>A | 1646呎 (4+房)
 $7911万
 $48,062/呎
-(19年-02月)</t>
+(19年-02月-17日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -14412,7 +18780,7 @@
           <t>B | 1606呎 (4+房)
 $6829万
 $42,522/呎
-(19年-08月)</t>
+(19年-08月-06日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -14420,7 +18788,7 @@
           <t>C | 1428呎 (4+房)
 $8145万
 $57,036/呎
-(16年-03月)</t>
+(16年-03月-24日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -14428,7 +18796,7 @@
           <t>D | 1142呎 (3房)
 $3482万
 $30,490/呎
-(16年-04月)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
     </row>
@@ -14443,7 +18811,7 @@
           <t>A | 1738呎 (4+房)
 $6652万
 $38,276/呎
-(16年-05月)</t>
+(16年-05月-22日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -14451,7 +18819,7 @@
           <t>B | 1708呎 (4+房)
 $6410万
 $37,530/呎
-(16年-04月)</t>
+(16年-04月-18日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -14459,7 +18827,7 @@
           <t>C | 1428呎 (4+房)
 $8145万
 $57,036/呎
-(16年-03月)</t>
+(16年-03月-24日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -14467,7 +18835,7 @@
           <t>D | 1142呎 (3房)
 $3419万
 $29,941/呎
-(16年-04月)</t>
+(16年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -14482,7 +18850,7 @@
           <t>A | 1738呎 (4+房)
 $6167万
 $35,482/呎
-(16年-04月)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -14490,7 +18858,7 @@
           <t>B | 1708呎 (4+房)
 $5942万
 $34,790/呎
-(16年-04月)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -14498,7 +18866,7 @@
           <t>C | 1428呎 (4+房)
 $3892万
 $27,256/呎
-(16年-05月)</t>
+(16年-05月-10日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -14506,7 +18874,7 @@
           <t>D | 1237呎 (3房)
 $3306万
 $26,729/呎
-(16年-05月)</t>
+(16年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -14521,7 +18889,7 @@
           <t>A | 1738呎 (4+房)
 $5080万
 $29,231/呎
-(16年-04月)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -14529,7 +18897,7 @@
           <t>B | 1708呎 (4+房)
 $4914万
 $28,771/呎
-(16年-04月)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -14537,7 +18905,7 @@
           <t>C | 1428呎 (4+房)
 $3764万
 $26,357/呎
-(16年-04月)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -14545,7 +18913,7 @@
           <t>D | 1237呎 (3房)
 $3197万
 $25,847/呎
-(16年-04月)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -14560,7 +18928,7 @@
           <t>A | 1738呎 (4+房)
 $4288万
 $24,671/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -14568,7 +18936,7 @@
           <t>B | 1708呎 (4+房)
 $4197万
 $24,571/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -14576,7 +18944,7 @@
           <t>C | 1428呎 (4+房)
 $3666万
 $25,672/呎
-(16年-04月)</t>
+(16年-04月-13日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -14584,7 +18952,7 @@
           <t>D | 1237呎 (3房)
 $3114万
 $25,175/呎
-(16年-04月)</t>
+(16年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -14599,7 +18967,7 @@
           <t>A | 1738呎 (4+房)
 $4159万
 $23,931/呎
-(16年-04月)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -14607,7 +18975,7 @@
           <t>B | 1708呎 (4+房)
 $4071万
 $23,833/呎
-(16年-04月)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -14615,7 +18983,7 @@
           <t>C | 1428呎 (4+房)
 $3593万
 $25,158/呎
-(16年-05月)</t>
+(16年-05月-04日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -14623,7 +18991,7 @@
           <t>D | 1237呎 (3房)
 $3036万
 $24,546/呎
-(16年-04月)</t>
+(16年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -14638,7 +19006,7 @@
           <t>A | 1738呎 (4+房)
 $3989万
 $22,950/呎
-(16年-04月)</t>
+(16年-04月-18日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -14646,7 +19014,7 @@
           <t>B | 1708呎 (4+房)
 $3904万
 $22,856/呎
-(16年-04月)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -14654,7 +19022,7 @@
           <t>C | 1428呎 (4+房)
 $3409万
 $23,875/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -14662,7 +19030,7 @@
           <t>D | 1237呎 (3房)
 $2881万
 $23,294/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -14677,7 +19045,7 @@
           <t>A | 1738呎 (4+房)
 $3206万
 $18,449/呎
-(16年-05月)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -14685,7 +19053,7 @@
           <t>B | 1708呎 (4+房)
 $2903万
 $16,996/呎
-(16年-04月)</t>
+(16年-04月-18日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -14693,7 +19061,7 @@
           <t>C | 1428呎 (4+房)
 $2617万
 $18,328/呎
-(16年-05月)</t>
+(16年-05月-05日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -14701,7 +19069,7 @@
           <t>D | 1237呎 (3房)
 $2320万
 $18,752/呎
-(16年-05月)</t>
+(16年-05月-08日)</t>
         </is>
       </c>
     </row>
@@ -14716,7 +19084,7 @@
           <t>A | 1630呎 (4+房)
 $3503万
 $21,490/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -14724,7 +19092,7 @@
           <t>B | 1691呎 (4+房)
 $2905万
 $17,177/呎
-(16年-04月)</t>
+(16年-04月-18日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -14732,7 +19100,7 @@
           <t>C | 1324呎 (4+房)
 $2597万
 $19,615/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -14740,7 +19108,7 @@
           <t>D | 1221呎 (3房)
 $2113万
 $17,309/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -14878,7 +19246,7 @@
           <t>A | 2681呎 (4+房)
 $15227万
 $56,795/呎
-(25年-11月)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -14887,7 +19255,7 @@
           <t>C | 1990呎 (3房)
 $12540万
 $63,015/呎
-(19年-11月)</t>
+(19年-11月-03日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -14895,7 +19263,7 @@
           <t>D | 2173呎 (3房)
 $7670万
 $35,298/呎
-(16年-05月)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -14912,7 +19280,7 @@
           <t>C | 2128呎 (3房)
 $8248万
 $38,761/呎
-(16年-05月)</t>
+(16年-05月-15日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr"/>
@@ -14920,52 +19288,52 @@
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
+          <t>22&amp;23</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 2265呎 (4+房)
+$15583万
+$68,797/呎
+(19年-07月-29日)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 2199呎 (4+房)
+$14260万
+$64,849/呎
+(19年-02月-20日)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr"/>
+      <c r="C8" s="21" t="inlineStr"/>
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 1237呎 (3房)
 $3250万
 $26,273/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr">
+(24年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 1428呎 (4+房)
 $4251万
 $29,770/呎
-(16年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>22&amp;23</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>A | 2265呎 (4+房)
-$15583万
-$68,797/呎
-(19年-07月)</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>B | 2199呎 (4+房)
-$14260万
-$64,849/呎
-(19年-02月)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr"/>
-      <c r="E8" s="21" t="inlineStr"/>
+(16年-04月-26日)</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -14978,7 +19346,7 @@
           <t>A | 1708呎 (4+房)
 $7567万
 $44,304/呎
-(19年-02月)</t>
+(19年-02月-25日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -14986,7 +19354,7 @@
           <t>B | 1738呎 (4+房)
 $6650万
 $38,262/呎
-(16年-04月)</t>
+(16年-04月-24日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -14994,7 +19362,7 @@
           <t>C | 1237呎 (3房)
 $7133万
 $57,666/呎
-(16年-03月)</t>
+(16年-03月-31日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -15002,7 +19370,7 @@
           <t>D | 1428呎 (4+房)
 $4238万
 $29,681/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -15017,7 +19385,7 @@
           <t>A | 1708呎 (4+房)
 $7472万
 $43,746/呎
-(19年-01月)</t>
+(19年-01月-30日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -15025,7 +19393,7 @@
           <t>B | 1738呎 (4+房)
 $6532万
 $37,585/呎
-(16年-05月)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -15033,7 +19401,7 @@
           <t>C | 1237呎 (3房)
 $3556万
 $28,747/呎
-(16年-04月)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -15041,7 +19409,7 @@
           <t>D | 1428呎 (4+房)
 $4226万
 $29,592/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -15056,7 +19424,7 @@
           <t>A | 1708呎 (4+房)
 $6764万
 $39,600/呎
-(19年-01月)</t>
+(19年-01月-24日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -15064,7 +19432,7 @@
           <t>B | 1738呎 (4+房)
 $6417万
 $36,921/呎
-(16年-05月)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -15072,7 +19440,7 @@
           <t>C | 1237呎 (3房)
 $3549万
 $28,689/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -15080,7 +19448,7 @@
           <t>D | 1428呎 (4+房)
 $4213万
 $29,503/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -15095,7 +19463,7 @@
           <t>A | 1708呎 (4+房)
 $13498万
 $79,030/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -15103,7 +19471,7 @@
           <t>B | 1738呎 (4+房)
 $13498万
 $77,666/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -15111,7 +19479,7 @@
           <t>C | 1237呎 (3房)
 $3549万
 $28,689/呎
-(16年-05月)</t>
+(16年-05月-03日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -15119,7 +19487,7 @@
           <t>D | 1428呎 (4+房)
 $4213万
 $29,503/呎
-(16年-05月)</t>
+(16年-05月-08日)</t>
         </is>
       </c>
     </row>
@@ -15134,7 +19502,7 @@
           <t>A | 1708呎 (4+房)
 $6662万
 $39,006/呎
-(23年-05月)</t>
+(23年-05月-04日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -15142,7 +19510,7 @@
           <t>B | 1738呎 (4+房)
 $6192万
 $35,627/呎
-(16年-04月)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -15150,7 +19518,7 @@
           <t>C | 1237呎 (3房)
 $3535万
 $28,575/呎
-(16年-04月)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -15158,7 +19526,7 @@
           <t>D | 1428呎 (4+房)
 $4188万
 $29,328/呎
-(16年-04月)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -15173,7 +19541,7 @@
           <t>A | 1708呎 (4+房)
 $6663万
 $39,009/呎
-(19年-01月)</t>
+(19年-01月-20日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -15181,7 +19549,7 @@
           <t>B | 1738呎 (4+房)
 $6082万
 $34,997/呎
-(16年-05月)</t>
+(16年-05月-15日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -15189,7 +19557,7 @@
           <t>C | 1237呎 (3房)
 $3528万
 $28,518/呎
-(16年-04月)</t>
+(16年-04月-25日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -15197,7 +19565,7 @@
           <t>D | 1428呎 (4+房)
 $4175万
 $29,240/呎
-(16年-04月)</t>
+(16年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -15212,7 +19580,7 @@
           <t>A | 1708呎 (4+房)
 $6483万
 $37,957/呎
-(19年-01月)</t>
+(19年-01月-17日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -15220,7 +19588,7 @@
           <t>B | 1738呎 (4+房)
 $6064万
 $34,892/呎
-(16年-04月)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -15228,7 +19596,7 @@
           <t>C | 1237呎 (3房)
 $3517万
 $28,432/呎
-(16年-04月)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -15236,7 +19604,7 @@
           <t>D | 1428呎 (4+房)
 $4163万
 $29,152/呎
-(16年-05月)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -15251,7 +19619,7 @@
           <t>A | 1708呎 (4+房)
 $6290万
 $36,827/呎
-(16年-05月)</t>
+(16年-05月-08日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -15259,7 +19627,7 @@
           <t>B | 1738呎 (4+房)
 $5864万
 $33,740/呎
-(16年-04月)</t>
+(16年-04月-24日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -15267,7 +19635,7 @@
           <t>C | 1237呎 (3房)
 $3454万
 $27,921/呎
-(16年-05月)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -15275,7 +19643,7 @@
           <t>D | 1428呎 (4+房)
 $4067万
 $28,482/呎
-(16年-04月)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -15290,7 +19658,7 @@
           <t>A | 1708呎 (4+房)
 $5890万
 $34,483/呎
-(19年-01月)</t>
+(19年-01月-21日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -15298,7 +19666,7 @@
           <t>B | 1738呎 (4+房)
 $5436万
 $31,277/呎
-(16年-04月)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -15306,7 +19674,7 @@
           <t>C | 1237呎 (3房)
 $3340万
 $26,999/呎
-(16年-05月)</t>
+(16年-05月-04日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -15314,7 +19682,7 @@
           <t>D | 1428呎 (4+房)
 $3933万
 $27,542/呎
-(16年-05月)</t>
+(16年-05月-04日)</t>
         </is>
       </c>
     </row>
@@ -15329,7 +19697,7 @@
           <t>A | 1708呎 (4+房)
 $5567万
 $32,593/呎
-(19年-03月)</t>
+(19年-03月-03日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -15337,7 +19705,7 @@
           <t>B | 1738呎 (4+房)
 $4441万
 $25,554/呎
-(16年-05月)</t>
+(16年-05月-02日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -15345,7 +19713,7 @@
           <t>C | 1237呎 (3房)
 $3263万
 $26,378/呎
-(16年-04月)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -15353,7 +19721,7 @@
           <t>D | 1428呎 (4+房)
 $3842万
 $26,908/呎
-(16年-04月)</t>
+(16年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -15368,7 +19736,7 @@
           <t>A | 1708呎 (4+房)
 $8063万
 $47,206/呎
-(16年-03月)</t>
+(16年-03月-31日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -15376,7 +19744,7 @@
           <t>B | 1738呎 (4+房)
 $8063万
 $46,391/呎
-(16年-03月)</t>
+(16年-03月-31日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -15384,7 +19752,7 @@
           <t>C | 1237呎 (3房)
 $3178万
 $25,692/呎
-(16年-04月)</t>
+(16年-04月-25日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -15392,7 +19760,7 @@
           <t>D | 1428呎 (4+房)
 $3743万
 $26,209/呎
-(16年-04月)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -15407,7 +19775,7 @@
           <t>A | 1708呎 (4+房)
 $5332万
 $31,220/呎
-(19年-01月)</t>
+(19年-01月-31日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -15415,7 +19783,7 @@
           <t>B | 1738呎 (4+房)
 $3891万
 $22,388/呎
-(16年-04月)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -15423,7 +19791,7 @@
           <t>C | 1237呎 (3房)
 $3115万
 $25,179/呎
-(16年-04月)</t>
+(16年-04月-24日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -15431,7 +19799,7 @@
           <t>D | 1428呎 (4+房)
 $3630万
 $25,422/呎
-(16年-04月)</t>
+(16年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -15446,7 +19814,7 @@
           <t>A | 1708呎 (4+房)
 $5188万
 $30,378/呎
-(19年-01月)</t>
+(19年-01月-10日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -15454,7 +19822,7 @@
           <t>B | 1738呎 (4+房)
 $3790万
 $21,806/呎
-(16年-04月)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -15462,7 +19830,7 @@
           <t>C | 1237呎 (3房)
 $2800万
 $22,635/呎
-(16年-04月)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -15470,7 +19838,7 @@
           <t>D | 1428呎 (4+房)
 $3227万
 $22,600/呎
-(16年-04月)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
     </row>
@@ -15485,7 +19853,7 @@
           <t>A | 1708呎 (4+房)
 $5049万
 $29,560/呎
-(19年-01月)</t>
+(19年-01月-14日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -15493,7 +19861,7 @@
           <t>B | 1738呎 (4+房)
 $3127万
 $17,990/呎
-(16年-04月)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -15501,7 +19869,7 @@
           <t>C | 1237呎 (3房)
 $2082万
 $16,831/呎
-(16年-04月)</t>
+(16年-04月-18日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -15509,7 +19877,7 @@
           <t>D | 1428呎 (4+房)
 $2499万
 $17,500/呎
-(16年-04月)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
     </row>
@@ -15524,7 +19892,7 @@
           <t>A | 1691呎 (4+房)
 $3166万
 $18,724/呎
-(16年-05月)</t>
+(16年-05月-03日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -15532,7 +19900,7 @@
           <t>B | 1722呎 (4+房)
 $3061万
 $17,778/呎
-(16年-05月)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -15540,7 +19908,7 @@
           <t>C | 1221呎 (3房)
 $2198万
 $18,005/呎
-(16年-04月)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -15548,7 +19916,7 @@
           <t>D | 1412呎 (4+房)
 $2421万
 $17,145/呎
-(16年-04月)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -15686,7 +20054,7 @@
           <t>A | 2733呎 (4+房)
 $21391万
 $78,270/呎
-(19年-02月)</t>
+(19年-02月-14日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -15695,7 +20063,7 @@
           <t>C | 2130呎 (4+房)
 $9165万
 $43,028/呎
-(16年-04月)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -15703,7 +20071,7 @@
           <t>D | 2187呎 (4+房)
 $15180万
 $69,410/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -15718,7 +20086,7 @@
           <t>A | 1320呎 (4+房)
 $4308万
 $32,634/呎
-(16年-05月)</t>
+(16年-05月-08日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -15726,7 +20094,7 @@
           <t>B | 1316呎 (4+房)
 $3998万
 $30,381/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -15734,7 +20102,7 @@
           <t>C | 2044呎 (3房)
 $12860万
 $62,916/呎
-(20年-02月)</t>
+(20年-02月-20日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr"/>
@@ -15750,7 +20118,7 @@
           <t>A | 1320呎 (4+房)
 $4295万
 $32,535/呎
-(16年-05月)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -15758,7 +20126,7 @@
           <t>B | 1221呎 (4+房)
 $3947万
 $32,325/呎
-(16年-05月)</t>
+(16年-05月-04日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -15766,7 +20134,7 @@
           <t>C | 1723呎 (4+房)
 $7074万
 $41,056/呎
-(16年-04月)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -15774,7 +20142,7 @@
           <t>D | 1160呎 (3房)
 $3862万
 $33,292/呎
-(16年-05月)</t>
+(16年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -15789,7 +20157,7 @@
           <t>A | 1320呎 (4+房)
 $4273万
 $32,373/呎
-(16年-05月)</t>
+(16年-05月-11日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -15797,7 +20165,7 @@
           <t>B | 1221呎 (4+房)
 $3896万
 $31,910/呎
-(16年-04月)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -15805,7 +20173,7 @@
           <t>C | 1723呎 (4+房)
 $7144万
 $41,465/呎
-(19年-01月)</t>
+(19年-01月-30日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -15813,7 +20181,7 @@
           <t>D | 1160呎 (3房)
 $3841万
 $33,110/呎
-(16年-05月)</t>
+(16年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -15828,7 +20196,7 @@
           <t>A | 1320呎 (4+房)
 $4190万
 $31,739/呎
-(16年-04月)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -15836,7 +20204,7 @@
           <t>B | 1316呎 (4+房)
 $7643万
 $58,079/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -15844,7 +20212,7 @@
           <t>C | 1723呎 (4+房)
 $6358万
 $36,904/呎
-(19年-01月)</t>
+(19年-01月-14日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -15852,7 +20220,7 @@
           <t>D | 1160呎 (3房)
 $3820万
 $32,929/呎
-(16年-05月)</t>
+(16年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -15867,7 +20235,7 @@
           <t>A | 1320呎 (4+房)
 $4196万
 $31,792/呎
-(16年-05月)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -15875,7 +20243,7 @@
           <t>B | 1316呎 (4+房)
 $3797万
 $28,851/呎
-(16年-05月)</t>
+(16年-05月-08日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -15883,7 +20251,7 @@
           <t>C | 1723呎 (4+房)
 $5342万
 $31,006/呎
-(24年-06月)</t>
+(24年-06月-23日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -15891,7 +20259,7 @@
           <t>D | 1160呎 (3房)
 $7643万
 $65,889/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -15906,7 +20274,7 @@
           <t>A | 1320呎 (4+房)
 $4155万
 $31,477/呎
-(16年-05月)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -15914,7 +20282,7 @@
           <t>B | 1316呎 (4+房)
 $3759万
 $28,566/呎
-(16年-05月)</t>
+(16年-05月-08日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -15922,7 +20290,7 @@
           <t>C | 1723呎 (4+房)
 $6268万
 $36,377/呎
-(19年-01月)</t>
+(19年-01月-06日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -15930,7 +20298,7 @@
           <t>D | 1160呎 (3房)
 $3782万
 $32,601/呎
-(16年-05月)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -15945,7 +20313,7 @@
           <t>A | 1320呎 (4+房)
 $4011万
 $30,383/呎
-(16年-05月)</t>
+(16年-05月-04日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -15953,7 +20321,7 @@
           <t>B | 1221呎 (4+房)
 $3700万
 $30,303/呎
-(16年-05月)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -15961,7 +20329,7 @@
           <t>C | 1723呎 (4+房)
 $6451万
 $37,442/呎
-(19年-01月)</t>
+(19年-01月-16日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -15969,7 +20337,7 @@
           <t>D | 1160呎 (3房)
 $3653万
 $31,491/呎
-(16年-05月)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -15984,7 +20352,7 @@
           <t>A | 1320呎 (4+房)
 $3940万
 $29,846/呎
-(16年-05月)</t>
+(16年-05月-05日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -15992,7 +20360,7 @@
           <t>B | 1316呎 (4+房)
 $3653万
 $27,755/呎
-(16年-05月)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -16000,7 +20368,7 @@
           <t>C | 1723呎 (4+房)
 $6802万
 $39,477/呎
-(19年-01月)</t>
+(19年-01月-16日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -16008,7 +20376,7 @@
           <t>D | 1160呎 (3房)
 $3540万
 $30,514/呎
-(16年-05月)</t>
+(16年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -16023,7 +20391,7 @@
           <t>A | 1320呎 (4+房)
 $3928万
 $29,756/呎
-(16年-05月)</t>
+(16年-05月-04日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -16031,7 +20399,7 @@
           <t>B | 1316呎 (4+房)
 $3642万
 $27,672/呎
-(16年-05月)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -16039,7 +20407,7 @@
           <t>C | 1723呎 (4+房)
 $5814万
 $33,745/呎
-(19年-01月)</t>
+(19年-01月-06日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -16047,7 +20415,7 @@
           <t>D | 1065呎 (3房)
 $3529万
 $33,136/呎
-(16年-05月)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -16062,7 +20430,7 @@
           <t>A | 1320呎 (4+房)
 $3837万
 $29,072/呎
-(16年-04月)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -16070,7 +20438,7 @@
           <t>B | 1316呎 (4+房)
 $3576万
 $27,174/呎
-(16年-04月)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -16078,7 +20446,7 @@
           <t>C | 1723呎 (4+房)
 $5815万
 $33,750/呎
-(19年-01月)</t>
+(19年-01月-16日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -16086,7 +20454,7 @@
           <t>D | 1160呎 (3房)
 $3501万
 $30,179/呎
-(16年-05月)</t>
+(16年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -16101,7 +20469,7 @@
           <t>A | 1320呎 (4+房)
 $3711万
 $28,112/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -16109,7 +20477,7 @@
           <t>B | 1316呎 (4+房)
 $3512万
 $26,685/呎
-(16年-04月)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -16117,7 +20485,7 @@
           <t>C | 1723呎 (4+房)
 $5663万
 $32,869/呎
-(16年-05月)</t>
+(16年-05月-08日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -16125,7 +20493,7 @@
           <t>D | 1160呎 (3房)
 $3403万
 $29,337/呎
-(16年-05月)</t>
+(16年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -16140,7 +20508,7 @@
           <t>A | 1320呎 (4+房)
 $3477万
 $26,341/呎
-(16年-05月)</t>
+(16年-05月-11日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -16148,7 +20516,7 @@
           <t>B | 1221呎 (4+房)
 $3361万
 $27,524/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -16156,7 +20524,7 @@
           <t>C | 1723呎 (4+房)
 $5448万
 $31,620/呎
-(16年-05月)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -16164,7 +20532,7 @@
           <t>D | 1065呎 (3房)
 $3308万
 $31,060/呎
-(16年-05月)</t>
+(16年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -16179,7 +20547,7 @@
           <t>A | 1320呎 (4+房)
 $3317万
 $25,130/呎
-(16年-05月)</t>
+(16年-05月-15日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -16187,7 +20555,7 @@
           <t>B | 1316呎 (4+房)
 $3139万
 $23,852/呎
-(16年-05月)</t>
+(16年-05月-02日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -16195,7 +20563,7 @@
           <t>C | 1723呎 (4+房)
 $5279万
 $30,640/呎
-(16年-05月)</t>
+(16年-05月-19日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -16203,7 +20571,7 @@
           <t>D | 1160呎 (3房)
 $3156万
 $27,204/呎
-(16年-05月)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -16218,7 +20586,7 @@
           <t>A | 1320呎 (4+房)
 $3085万
 $23,371/呎
-(16年-05月)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -16226,7 +20594,7 @@
           <t>B | 1316呎 (4+房)
 $2919万
 $22,182/呎
-(16年-04月)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -16234,7 +20602,7 @@
           <t>C | 1723呎 (4+房)
 $5534万
 $32,120/呎
-(19年-01月)</t>
+(19年-01月-15日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -16242,7 +20610,7 @@
           <t>D | 1065呎 (3房)
 $3045万
 $28,596/呎
-(16年-05月)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -16257,7 +20625,7 @@
           <t>A | 1320呎 (4+房)
 $3066万
 $23,230/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -16265,7 +20633,7 @@
           <t>B | 1316呎 (4+房)
 $2902万
 $22,049/呎
-(16年-04月)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -16273,7 +20641,7 @@
           <t>C | 1723呎 (4+房)
 $4871万
 $28,272/呎
-(19年-01月)</t>
+(19年-01月-03日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -16281,7 +20649,7 @@
           <t>D | 1160呎 (3房)
 $2875万
 $24,784/呎
-(16年-05月)</t>
+(16年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -16296,7 +20664,7 @@
           <t>A | 1320呎 (4+房)
 $2529万
 $19,162/呎
-(16年-05月)</t>
+(16年-05月-18日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -16304,7 +20672,7 @@
           <t>B | 1221呎 (4+房)
 $2211万
 $18,105/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -16312,7 +20680,7 @@
           <t>C | 1723呎 (4+房)
 $3896万
 $22,610/呎
-(16年-05月)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -16320,7 +20688,7 @@
           <t>D | 1160呎 (3房)
 $2329万
 $20,075/呎
-(16年-05月)</t>
+(16年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -16335,7 +20703,7 @@
           <t>A | 1150呎 (4+房)
 $3623万
 $31,505/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -16343,7 +20711,7 @@
           <t>B | 1300呎 (4+房)
 $2506万
 $19,276/呎
-(16年-05月)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -16351,7 +20719,7 @@
           <t>C | 1723呎 (3房)
 $3909万
 $22,690/呎
-(16年-05月)</t>
+(16年-05月-15日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -16359,7 +20727,7 @@
           <t>D | 1143呎 (3房)
 $2173万
 $19,011/呎
-(16年-05月)</t>
+(16年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -16374,7 +20742,7 @@
           <t>A | 1929呎 (3房)
 $4593万
 $23,811/呎
-(16年-04月)</t>
+(16年-04月-07日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -16382,7 +20750,7 @@
           <t>B | 1970呎 (2房)
 $6277万
 $31,865/呎
-(16年-05月)</t>
+(16年-05月-18日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr"/>

--- a/files/九龙-何文田-天铸 (第2期).xlsx
+++ b/files/九龙-何文田-天铸 (第2期).xlsx
@@ -18480,10 +18480,35 @@
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 1428呎 (4+房)
+$4207万
+$29,461/呎
+(16年-04月-19日)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 1237呎 (3房)
+$3534万
+$28,573/呎
+(16年-04月-19日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
           <t>22&amp;23</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 2199呎 (4+房)
 $11391万
@@ -18491,7 +18516,7 @@
 (24年-04月-28日)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 2361呎 (4+房)
 $12169万
@@ -18499,33 +18524,8 @@
 (16年-04月-21日)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr"/>
-      <c r="C8" s="21" t="inlineStr"/>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>C | 1428呎 (4+房)
-$4207万
-$29,461/呎
-(16年-04月-19日)</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>D | 1237呎 (3房)
-$3534万
-$28,573/呎
-(16年-04月-19日)</t>
-        </is>
-      </c>
+      <c r="D8" s="21" t="inlineStr"/>
+      <c r="E8" s="21" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -19288,10 +19288,35 @@
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3250万
+$26,273/呎
+(24年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$4251万
+$29,770/呎
+(16年-04月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
           <t>22&amp;23</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 2265呎 (4+房)
 $15583万
@@ -19299,7 +19324,7 @@
 (19年-07月-29日)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 2199呎 (4+房)
 $14260万
@@ -19307,33 +19332,8 @@
 (19年-02月-20日)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr"/>
-      <c r="C8" s="21" t="inlineStr"/>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3250万
-$26,273/呎
-(24年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$4251万
-$29,770/呎
-(16年-04月-26日)</t>
-        </is>
-      </c>
+      <c r="D8" s="21" t="inlineStr"/>
+      <c r="E8" s="21" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">

--- a/files/九龙-何文田-天铸 (第2期).xlsx
+++ b/files/九龙-何文田-天铸 (第2期).xlsx
@@ -17696,7 +17696,7 @@
           <t>C | 2503呎 (4+房)
 $8719万
 $34,834/呎
-(16年-04月-07日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr"/>
@@ -17720,7 +17720,7 @@
           <t>B | 2442呎 (4+房)
 $13076万
 $53,546/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -17728,7 +17728,7 @@
           <t>C | 2489呎 (4+房)
 $10247万
 $41,169/呎
-(16年-04月-20日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr"/>
@@ -17744,7 +17744,7 @@
           <t>A | 1910呎 (4+房)
 $7752万
 $40,584/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -17752,7 +17752,7 @@
           <t>B | 1731呎 (4+房)
 $7478万
 $43,203/呎
-(25年-10月-27日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -17760,7 +17760,7 @@
           <t>C | 1154呎 (3房)
 $3469万
 $30,058/呎
-(16年-05月-12日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -17768,7 +17768,7 @@
           <t>D | 994呎 (3房)
 $2977万
 $29,953/呎
-(16年-05月-08日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -17783,7 +17783,7 @@
           <t>A | 1910呎 (4+房)
 $8480万
 $44,397/呎
-(19年-04月-03日)</t>
+(19年-04月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -17791,7 +17791,7 @@
           <t>B | 1823呎 (4+房)
 $9466万
 $51,927/呎
-(16年-05月-17日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -17799,7 +17799,7 @@
           <t>C | 1154呎 (3房)
 $6396万
 $55,425/呎
-(16年-04月-14日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -17807,7 +17807,7 @@
           <t>D | 994呎 (3房)
 $6396万
 $64,346/呎
-(16年-04月-14日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -17822,7 +17822,7 @@
           <t>A | 1910呎 (4+房)
 $7227万
 $37,837/呎
-(25年-08月-19日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -17830,7 +17830,7 @@
           <t>B | 1731呎 (4+房)
 $7854万
 $45,373/呎
-(23年-03月-20日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -17838,7 +17838,7 @@
           <t>C | 1154呎 (3房)
 $3377万
 $29,263/呎
-(16年-04月-07日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -17846,7 +17846,7 @@
           <t>D | 994呎 (3房)
 $2968万
 $29,863/呎
-(16年-05月-05日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -17861,7 +17861,7 @@
           <t>A | 1910呎 (4+房)
 $8610万
 $45,078/呎
-(23年-03月-05日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -17869,7 +17869,7 @@
           <t>B | 1731呎 (4+房)
 $7754万
 $44,794/呎
-(23年-04月-03日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -17877,7 +17877,7 @@
           <t>C | 1154呎 (3房)
 $3364万
 $29,146/呎
-(16年-04月-28日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -17885,7 +17885,7 @@
           <t>D | 994呎 (3房)
 $2951万
 $29,685/呎
-(16年-05月-09日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -17900,7 +17900,7 @@
           <t>A | 1910呎 (4+房)
 $8572万
 $44,880/呎
-(23年-03月-02日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -17908,7 +17908,7 @@
           <t>B | 1823呎 (4+房)
 $8529万
 $46,787/呎
-(16年-05月-08日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -17916,7 +17916,7 @@
           <t>C | 1154呎 (3房)
 $3357万
 $29,088/呎
-(16年-05月-15日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -17924,7 +17924,7 @@
           <t>D | 994呎 (3房)
 $2942万
 $29,596/呎
-(16年-05月-15日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -17939,7 +17939,7 @@
           <t>A | 1910呎 (4+房)
 $7672万
 $40,169/呎
-(19年-04月-03日)</t>
+(19年-04月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -17947,7 +17947,7 @@
           <t>B | 1823呎 (4+房)
 $8333万
 $45,711/呎
-(16年-05月-17日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -17955,7 +17955,7 @@
           <t>C | 1154呎 (3房)
 $3347万
 $29,001/呎
-(16年-05月-17日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -17963,7 +17963,7 @@
           <t>D | 994呎 (3房)
 $2933万
 $29,507/呎
-(16年-05月-11日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -17978,7 +17978,7 @@
           <t>A | 2019呎 (4+房)
 $8076万
 $40,000/呎
-(19年-09月-22日)</t>
+(19年-09月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -17986,7 +17986,7 @@
           <t>B | 1823呎 (4+房)
 $7295万
 $40,018/呎
-(21年-11月-16日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -17994,7 +17994,7 @@
           <t>C | 1154呎 (3房)
 $3286万
 $28,479/呎
-(16年-05月-02日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -18002,7 +18002,7 @@
           <t>D | 994呎 (3房)
 $2895万
 $29,124/呎
-(16年-05月-10日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -18017,7 +18017,7 @@
           <t>A | 1910呎 (4+房)
 $8087万
 $42,338/呎
-(19年-04月-09日)</t>
+(19年-04月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -18025,7 +18025,7 @@
           <t>B | 1823呎 (4+房)
 $6927万
 $38,000/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -18033,7 +18033,7 @@
           <t>C | 1154呎 (3房)
 $3211万
 $27,824/呎
-(16年-05月-02日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -18041,7 +18041,7 @@
           <t>D | 994呎 (3房)
 $2857万
 $28,745/呎
-(16年-05月-17日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -18056,7 +18056,7 @@
           <t>A | 2019呎 (4+房)
 $7207万
 $35,698/呎
-(16年-05月-09日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -18064,7 +18064,7 @@
           <t>B | 1823呎 (4+房)
 $15180万
 $83,269/呎
-(16年-04月-14日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -18072,7 +18072,7 @@
           <t>C | 1154呎 (3房)
 $3137万
 $27,184/呎
-(16年-04月-26日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -18080,7 +18080,7 @@
           <t>D | 994呎 (3房)
 $2792万
 $28,084/呎
-(16年-05月-09日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -18095,7 +18095,7 @@
           <t>A | 2019呎 (4+房)
 $5588万
 $27,679/呎
-(16年-04月-25日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -18103,7 +18103,7 @@
           <t>B | 1823呎 (4+房)
 $5001万
 $27,433/呎
-(16年-05月-04日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -18111,7 +18111,7 @@
           <t>C | 1154呎 (3房)
 $3008万
 $26,069/呎
-(16年-04月-28日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -18119,7 +18119,7 @@
           <t>D | 994呎 (3房)
 $2705万
 $27,213/呎
-(16年-05月-16日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -18134,7 +18134,7 @@
           <t>A | 1910呎 (4+房)
 $5588万
 $29,257/呎
-(16年-05月-17日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -18142,7 +18142,7 @@
           <t>B | 1823呎 (4+房)
 $5001万
 $27,435/呎
-(16年-05月-17日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -18150,7 +18150,7 @@
           <t>C | 1154呎 (3房)
 $2858万
 $24,766/呎
-(16年-05月-05日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -18158,7 +18158,7 @@
           <t>D | 994呎 (3房)
 $2637万
 $26,533/呎
-(16年-05月-09日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -18173,7 +18173,7 @@
           <t>A | 2019呎 (4+房)
 $4703万
 $23,292/呎
-(16年-04月-26日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -18181,7 +18181,7 @@
           <t>B | 1823呎 (4+房)
 $4234万
 $23,227/呎
-(16年-04月-26日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -18189,7 +18189,7 @@
           <t>C | 1154呎 (3房)
 $2741万
 $23,751/呎
-(16年-04月-28日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -18197,7 +18197,7 @@
           <t>D | 994呎 (3房)
 $2529万
 $25,445/呎
-(16年-05月-12日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -18212,7 +18212,7 @@
           <t>A | 2019呎 (4+房)
 $6379万
 $31,596/呎
-(16年-03月-31日)</t>
+(16年-03月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -18220,7 +18220,7 @@
           <t>B | 1823呎 (4+房)
 $6379万
 $34,993/呎
-(16年-03月-31日)</t>
+(16年-03月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -18228,7 +18228,7 @@
           <t>C | 1154呎 (3房)
 $2289万
 $19,832/呎
-(16年-05月-12日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -18236,7 +18236,7 @@
           <t>D | 994呎 (3房)
 $2036万
 $20,483/呎
-(16年-05月-12日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -18251,7 +18251,7 @@
           <t>A | 2019呎 (4+房)
 $3613万
 $17,895/呎
-(16年-04月-18日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -18259,7 +18259,7 @@
           <t>B | 1807呎 (4+房)
 $3006万
 $16,637/呎
-(16年-05月-08日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -18267,7 +18267,7 @@
           <t>C | 1045呎 (3房)
 $2070万
 $19,812/呎
-(16年-04月-24日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -18275,7 +18275,7 @@
           <t>D | 863呎 (3房)
 $1833万
 $21,235/呎
-(16年-05月-09日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -18290,7 +18290,7 @@
           <t>A | 2065呎 (3房)
 $4674万
 $22,634/呎
-(16年-04月-26日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -18298,7 +18298,7 @@
           <t>B | 2337呎 (4+房)
 $5436万
 $23,262/呎
-(16年-04月-14日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr"/>
@@ -18438,7 +18438,7 @@
           <t>A | 2681呎 (4+房)
 $14831万
 $55,319/呎
-(25年-08月-11日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -18447,7 +18447,7 @@
           <t>C | 2079呎 (3房)
 $7509万
 $36,121/呎
-(16年-04月-25日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -18455,7 +18455,7 @@
           <t>D | 2090呎 (3房)
 $7751万
 $37,088/呎
-(16年-05月-03日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -18472,7 +18472,7 @@
           <t>C | 2026呎 (4+房)
 $8348万
 $41,206/呎
-(16年-05月-10日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr"/>
@@ -18490,7 +18490,7 @@
           <t>C | 1428呎 (4+房)
 $4207万
 $29,461/呎
-(16年-04月-19日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -18498,7 +18498,7 @@
           <t>D | 1237呎 (3房)
 $3534万
 $28,573/呎
-(16年-04月-19日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -18513,7 +18513,7 @@
           <t>A | 2199呎 (4+房)
 $11391万
 $51,801/呎
-(24年-04月-28日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -18521,7 +18521,7 @@
           <t>B | 2361呎 (4+房)
 $12169万
 $51,540/呎
-(16年-04月-21日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr"/>
@@ -18538,7 +18538,7 @@
           <t>A | 1738呎 (4+房)
 $7820万
 $44,994/呎
-(16年-05月-05日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -18546,7 +18546,7 @@
           <t>B | 1606呎 (4+房)
 $7198万
 $44,819/呎
-(16年-04月-20日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -18554,7 +18554,7 @@
           <t>C | 1428呎 (4+房)
 $4194万
 $29,373/呎
-(16年-04月-17日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -18562,7 +18562,7 @@
           <t>D | 1237呎 (3房)
 $3527万
 $28,516/呎
-(16年-04月-17日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -18577,7 +18577,7 @@
           <t>A | 1646呎 (4+房)
 $8182万
 $49,711/呎
-(19年-01月-27日)</t>
+(19年-01月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -18585,7 +18585,7 @@
           <t>B | 1606呎 (4+房)
 $7464万
 $46,475/呎
-(19年-03月-03日)</t>
+(19年-03月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -18593,7 +18593,7 @@
           <t>C | 1428呎 (4+房)
 $8351万
 $58,483/呎
-(16年-03月-24日)</t>
+(16年-03月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -18601,7 +18601,7 @@
           <t>D | 1237呎 (3房)
 $3520万
 $28,459/呎
-(16年-04月-12日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -18616,7 +18616,7 @@
           <t>A | 1738呎 (4+房)
 $7583万
 $43,633/呎
-(16年-04月-19日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -18624,7 +18624,7 @@
           <t>B | 1708呎 (4+房)
 $6946万
 $40,665/呎
-(16年-05月-08日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -18632,7 +18632,7 @@
           <t>C | 1428呎 (4+房)
 $8351万
 $58,483/呎
-(16年-03月-24日)</t>
+(16年-03月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -18640,7 +18640,7 @@
           <t>D | 1237呎 (3房)
 $3513万
 $28,402/呎
-(16年-04月-17日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -18655,7 +18655,7 @@
           <t>A | 1646呎 (4+房)
 $6398万
 $38,870/呎
-(24年-10月-14日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -18663,7 +18663,7 @@
           <t>B | 1606呎 (4+房)
 $7068万
 $44,010/呎
-(26年-01月-06日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -18671,7 +18671,7 @@
           <t>C | 1428呎 (4+房)
 $4169万
 $29,198/呎
-(16年-04月-17日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -18679,7 +18679,7 @@
           <t>D | 1237呎 (3房)
 $3513万
 $28,402/呎
-(16年-04月-17日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -18694,7 +18694,7 @@
           <t>A | 1738呎 (4+房)
 $7318万
 $42,104/呎
-(16年-04月-19日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -18702,7 +18702,7 @@
           <t>B | 1708呎 (4+房)
 $6735万
 $39,433/呎
-(16年-05月-11日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -18710,7 +18710,7 @@
           <t>C | 1428呎 (4+房)
 $4145万
 $29,024/呎
-(16年-04月-17日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -18718,7 +18718,7 @@
           <t>D | 1237呎 (3房)
 $3499万
 $28,289/呎
-(16年-04月-17日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -18733,7 +18733,7 @@
           <t>A | 1738呎 (4+房)
 $7188万
 $41,360/呎
-(16年-04月-21日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -18741,7 +18741,7 @@
           <t>B | 1708呎 (4+房)
 $6649万
 $38,927/呎
-(16年-04月-21日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -18749,7 +18749,7 @@
           <t>C | 1428呎 (4+房)
 $4132万
 $28,937/呎
-(16年-04月-19日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -18757,7 +18757,7 @@
           <t>D | 1237呎 (3房)
 $3492万
 $28,233/呎
-(16年-04月-19日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -18772,7 +18772,7 @@
           <t>A | 1646呎 (4+房)
 $7911万
 $48,062/呎
-(19年-02月-17日)</t>
+(19年-02月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -18780,7 +18780,7 @@
           <t>B | 1606呎 (4+房)
 $6829万
 $42,522/呎
-(19年-08月-06日)</t>
+(19年-08月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -18788,7 +18788,7 @@
           <t>C | 1428呎 (4+房)
 $8145万
 $57,036/呎
-(16年-03月-24日)</t>
+(16年-03月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -18796,7 +18796,7 @@
           <t>D | 1142呎 (3房)
 $3482万
 $30,490/呎
-(16年-04月-19日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -18811,7 +18811,7 @@
           <t>A | 1738呎 (4+房)
 $6652万
 $38,276/呎
-(16年-05月-22日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -18819,7 +18819,7 @@
           <t>B | 1708呎 (4+房)
 $6410万
 $37,530/呎
-(16年-04月-18日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -18827,7 +18827,7 @@
           <t>C | 1428呎 (4+房)
 $8145万
 $57,036/呎
-(16年-03月-24日)</t>
+(16年-03月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -18835,7 +18835,7 @@
           <t>D | 1142呎 (3房)
 $3419万
 $29,941/呎
-(16年-04月-18日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -18850,7 +18850,7 @@
           <t>A | 1738呎 (4+房)
 $6167万
 $35,482/呎
-(16年-04月-28日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -18858,7 +18858,7 @@
           <t>B | 1708呎 (4+房)
 $5942万
 $34,790/呎
-(16年-04月-19日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -18866,7 +18866,7 @@
           <t>C | 1428呎 (4+房)
 $3892万
 $27,256/呎
-(16年-05月-10日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -18874,7 +18874,7 @@
           <t>D | 1237呎 (3房)
 $3306万
 $26,729/呎
-(16年-05月-03日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
           <t>A | 1738呎 (4+房)
 $5080万
 $29,231/呎
-(16年-04月-20日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -18897,7 +18897,7 @@
           <t>B | 1708呎 (4+房)
 $4914万
 $28,771/呎
-(16年-04月-20日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -18905,7 +18905,7 @@
           <t>C | 1428呎 (4+房)
 $3764万
 $26,357/呎
-(16年-04月-20日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -18913,7 +18913,7 @@
           <t>D | 1237呎 (3房)
 $3197万
 $25,847/呎
-(16年-04月-20日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -18928,7 +18928,7 @@
           <t>A | 1738呎 (4+房)
 $4288万
 $24,671/呎
-(16年-04月-14日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -18936,7 +18936,7 @@
           <t>B | 1708呎 (4+房)
 $4197万
 $24,571/呎
-(16年-04月-14日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -18944,7 +18944,7 @@
           <t>C | 1428呎 (4+房)
 $3666万
 $25,672/呎
-(16年-04月-13日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -18952,7 +18952,7 @@
           <t>D | 1237呎 (3房)
 $3114万
 $25,175/呎
-(16年-04月-18日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -18967,7 +18967,7 @@
           <t>A | 1738呎 (4+房)
 $4159万
 $23,931/呎
-(16年-04月-21日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -18975,7 +18975,7 @@
           <t>B | 1708呎 (4+房)
 $4071万
 $23,833/呎
-(16年-04月-19日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -18983,7 +18983,7 @@
           <t>C | 1428呎 (4+房)
 $3593万
 $25,158/呎
-(16年-05月-04日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -18991,7 +18991,7 @@
           <t>D | 1237呎 (3房)
 $3036万
 $24,546/呎
-(16年-04月-25日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -19006,7 +19006,7 @@
           <t>A | 1738呎 (4+房)
 $3989万
 $22,950/呎
-(16年-04月-18日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -19014,7 +19014,7 @@
           <t>B | 1708呎 (4+房)
 $3904万
 $22,856/呎
-(16年-04月-21日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -19022,7 +19022,7 @@
           <t>C | 1428呎 (4+房)
 $3409万
 $23,875/呎
-(16年-04月-26日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -19030,7 +19030,7 @@
           <t>D | 1237呎 (3房)
 $2881万
 $23,294/呎
-(16年-04月-26日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -19045,7 +19045,7 @@
           <t>A | 1738呎 (4+房)
 $3206万
 $18,449/呎
-(16年-05月-16日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -19053,7 +19053,7 @@
           <t>B | 1708呎 (4+房)
 $2903万
 $16,996/呎
-(16年-04月-18日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -19061,7 +19061,7 @@
           <t>C | 1428呎 (4+房)
 $2617万
 $18,328/呎
-(16年-05月-05日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -19069,7 +19069,7 @@
           <t>D | 1237呎 (3房)
 $2320万
 $18,752/呎
-(16年-05月-08日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -19084,7 +19084,7 @@
           <t>A | 1630呎 (4+房)
 $3503万
 $21,490/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -19092,7 +19092,7 @@
           <t>B | 1691呎 (4+房)
 $2905万
 $17,177/呎
-(16年-04月-18日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -19100,7 +19100,7 @@
           <t>C | 1324呎 (4+房)
 $2597万
 $19,615/呎
-(16年-04月-26日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -19108,7 +19108,7 @@
           <t>D | 1221呎 (3房)
 $2113万
 $17,309/呎
-(16年-04月-26日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -19246,7 +19246,7 @@
           <t>A | 2681呎 (4+房)
 $15227万
 $56,795/呎
-(25年-11月-24日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -19255,7 +19255,7 @@
           <t>C | 1990呎 (3房)
 $12540万
 $63,015/呎
-(19年-11月-03日)</t>
+(19年-11月)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -19263,7 +19263,7 @@
           <t>D | 2173呎 (3房)
 $7670万
 $35,298/呎
-(16年-05月-16日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -19280,7 +19280,7 @@
           <t>C | 2128呎 (3房)
 $8248万
 $38,761/呎
-(16年-05月-15日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr"/>
@@ -19298,7 +19298,7 @@
           <t>C | 1237呎 (3房)
 $3250万
 $26,273/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -19306,7 +19306,7 @@
           <t>D | 1428呎 (4+房)
 $4251万
 $29,770/呎
-(16年-04月-26日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -19321,7 +19321,7 @@
           <t>A | 2265呎 (4+房)
 $15583万
 $68,797/呎
-(19年-07月-29日)</t>
+(19年-07月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -19329,7 +19329,7 @@
           <t>B | 2199呎 (4+房)
 $14260万
 $64,849/呎
-(19年-02月-20日)</t>
+(19年-02月)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr"/>
@@ -19346,7 +19346,7 @@
           <t>A | 1708呎 (4+房)
 $7567万
 $44,304/呎
-(19年-02月-25日)</t>
+(19年-02月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -19354,7 +19354,7 @@
           <t>B | 1738呎 (4+房)
 $6650万
 $38,262/呎
-(16年-04月-24日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -19362,7 +19362,7 @@
           <t>C | 1237呎 (3房)
 $7133万
 $57,666/呎
-(16年-03月-31日)</t>
+(16年-03月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -19370,7 +19370,7 @@
           <t>D | 1428呎 (4+房)
 $4238万
 $29,681/呎
-(16年-04月-26日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -19385,7 +19385,7 @@
           <t>A | 1708呎 (4+房)
 $7472万
 $43,746/呎
-(19年-01月-30日)</t>
+(19年-01月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -19393,7 +19393,7 @@
           <t>B | 1738呎 (4+房)
 $6532万
 $37,585/呎
-(16年-05月-16日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -19401,7 +19401,7 @@
           <t>C | 1237呎 (3房)
 $3556万
 $28,747/呎
-(16年-04月-20日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -19409,7 +19409,7 @@
           <t>D | 1428呎 (4+房)
 $4226万
 $29,592/呎
-(16年-04月-26日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -19424,7 +19424,7 @@
           <t>A | 1708呎 (4+房)
 $6764万
 $39,600/呎
-(19年-01月-24日)</t>
+(19年-01月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -19432,7 +19432,7 @@
           <t>B | 1738呎 (4+房)
 $6417万
 $36,921/呎
-(16年-05月-09日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -19440,7 +19440,7 @@
           <t>C | 1237呎 (3房)
 $3549万
 $28,689/呎
-(16年-04月-26日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -19448,7 +19448,7 @@
           <t>D | 1428呎 (4+房)
 $4213万
 $29,503/呎
-(16年-04月-26日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -19463,7 +19463,7 @@
           <t>A | 1708呎 (4+房)
 $13498万
 $79,030/呎
-(16年-04月-14日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -19471,7 +19471,7 @@
           <t>B | 1738呎 (4+房)
 $13498万
 $77,666/呎
-(16年-04月-14日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -19479,7 +19479,7 @@
           <t>C | 1237呎 (3房)
 $3549万
 $28,689/呎
-(16年-05月-03日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -19487,7 +19487,7 @@
           <t>D | 1428呎 (4+房)
 $4213万
 $29,503/呎
-(16年-05月-08日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -19502,7 +19502,7 @@
           <t>A | 1708呎 (4+房)
 $6662万
 $39,006/呎
-(23年-05月-04日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -19510,7 +19510,7 @@
           <t>B | 1738呎 (4+房)
 $6192万
 $35,627/呎
-(16年-04月-20日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -19518,7 +19518,7 @@
           <t>C | 1237呎 (3房)
 $3535万
 $28,575/呎
-(16年-04月-20日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -19526,7 +19526,7 @@
           <t>D | 1428呎 (4+房)
 $4188万
 $29,328/呎
-(16年-04月-20日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -19541,7 +19541,7 @@
           <t>A | 1708呎 (4+房)
 $6663万
 $39,009/呎
-(19年-01月-20日)</t>
+(19年-01月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -19549,7 +19549,7 @@
           <t>B | 1738呎 (4+房)
 $6082万
 $34,997/呎
-(16年-05月-15日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -19557,7 +19557,7 @@
           <t>C | 1237呎 (3房)
 $3528万
 $28,518/呎
-(16年-04月-25日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -19565,7 +19565,7 @@
           <t>D | 1428呎 (4+房)
 $4175万
 $29,240/呎
-(16年-04月-18日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -19580,7 +19580,7 @@
           <t>A | 1708呎 (4+房)
 $6483万
 $37,957/呎
-(19年-01月-17日)</t>
+(19年-01月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -19588,7 +19588,7 @@
           <t>B | 1738呎 (4+房)
 $6064万
 $34,892/呎
-(16年-04月-28日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -19596,7 +19596,7 @@
           <t>C | 1237呎 (3房)
 $3517万
 $28,432/呎
-(16年-04月-28日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -19604,7 +19604,7 @@
           <t>D | 1428呎 (4+房)
 $4163万
 $29,152/呎
-(16年-05月-16日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -19619,7 +19619,7 @@
           <t>A | 1708呎 (4+房)
 $6290万
 $36,827/呎
-(16年-05月-08日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -19627,7 +19627,7 @@
           <t>B | 1738呎 (4+房)
 $5864万
 $33,740/呎
-(16年-04月-24日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -19635,7 +19635,7 @@
           <t>C | 1237呎 (3房)
 $3454万
 $27,921/呎
-(16年-05月-12日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -19643,7 +19643,7 @@
           <t>D | 1428呎 (4+房)
 $4067万
 $28,482/呎
-(16年-04月-21日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -19658,7 +19658,7 @@
           <t>A | 1708呎 (4+房)
 $5890万
 $34,483/呎
-(19年-01月-21日)</t>
+(19年-01月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -19666,7 +19666,7 @@
           <t>B | 1738呎 (4+房)
 $5436万
 $31,277/呎
-(16年-04月-27日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -19674,7 +19674,7 @@
           <t>C | 1237呎 (3房)
 $3340万
 $26,999/呎
-(16年-05月-04日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -19682,7 +19682,7 @@
           <t>D | 1428呎 (4+房)
 $3933万
 $27,542/呎
-(16年-05月-04日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -19697,7 +19697,7 @@
           <t>A | 1708呎 (4+房)
 $5567万
 $32,593/呎
-(19年-03月-03日)</t>
+(19年-03月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -19705,7 +19705,7 @@
           <t>B | 1738呎 (4+房)
 $4441万
 $25,554/呎
-(16年-05月-02日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -19713,7 +19713,7 @@
           <t>C | 1237呎 (3房)
 $3263万
 $26,378/呎
-(16年-04月-19日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -19721,7 +19721,7 @@
           <t>D | 1428呎 (4+房)
 $3842万
 $26,908/呎
-(16年-04月-25日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -19736,7 +19736,7 @@
           <t>A | 1708呎 (4+房)
 $8063万
 $47,206/呎
-(16年-03月-31日)</t>
+(16年-03月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -19744,7 +19744,7 @@
           <t>B | 1738呎 (4+房)
 $8063万
 $46,391/呎
-(16年-03月-31日)</t>
+(16年-03月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -19752,7 +19752,7 @@
           <t>C | 1237呎 (3房)
 $3178万
 $25,692/呎
-(16年-04月-25日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -19760,7 +19760,7 @@
           <t>D | 1428呎 (4+房)
 $3743万
 $26,209/呎
-(16年-04月-20日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -19775,7 +19775,7 @@
           <t>A | 1708呎 (4+房)
 $5332万
 $31,220/呎
-(19年-01月-31日)</t>
+(19年-01月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -19783,7 +19783,7 @@
           <t>B | 1738呎 (4+房)
 $3891万
 $22,388/呎
-(16年-04月-21日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -19791,7 +19791,7 @@
           <t>C | 1237呎 (3房)
 $3115万
 $25,179/呎
-(16年-04月-24日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -19799,7 +19799,7 @@
           <t>D | 1428呎 (4+房)
 $3630万
 $25,422/呎
-(16年-04月-24日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -19814,7 +19814,7 @@
           <t>A | 1708呎 (4+房)
 $5188万
 $30,378/呎
-(19年-01月-10日)</t>
+(19年-01月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -19822,7 +19822,7 @@
           <t>B | 1738呎 (4+房)
 $3790万
 $21,806/呎
-(16年-04月-27日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -19830,7 +19830,7 @@
           <t>C | 1237呎 (3房)
 $2800万
 $22,635/呎
-(16年-04月-19日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -19838,7 +19838,7 @@
           <t>D | 1428呎 (4+房)
 $3227万
 $22,600/呎
-(16年-04月-19日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -19853,7 +19853,7 @@
           <t>A | 1708呎 (4+房)
 $5049万
 $29,560/呎
-(19年-01月-14日)</t>
+(19年-01月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -19861,7 +19861,7 @@
           <t>B | 1738呎 (4+房)
 $3127万
 $17,990/呎
-(16年-04月-19日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -19869,7 +19869,7 @@
           <t>C | 1237呎 (3房)
 $2082万
 $16,831/呎
-(16年-04月-18日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -19877,7 +19877,7 @@
           <t>D | 1428呎 (4+房)
 $2499万
 $17,500/呎
-(16年-04月-19日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -19892,7 +19892,7 @@
           <t>A | 1691呎 (4+房)
 $3166万
 $18,724/呎
-(16年-05月-03日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -19900,7 +19900,7 @@
           <t>B | 1722呎 (4+房)
 $3061万
 $17,778/呎
-(16年-05月-17日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -19908,7 +19908,7 @@
           <t>C | 1221呎 (3房)
 $2198万
 $18,005/呎
-(16年-04月-21日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -19916,7 +19916,7 @@
           <t>D | 1412呎 (4+房)
 $2421万
 $17,145/呎
-(16年-04月-21日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
           <t>A | 2733呎 (4+房)
 $21391万
 $78,270/呎
-(19年-02月-14日)</t>
+(19年-02月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -20063,7 +20063,7 @@
           <t>C | 2130呎 (4+房)
 $9165万
 $43,028/呎
-(16年-04月-21日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -20071,7 +20071,7 @@
           <t>D | 2187呎 (4+房)
 $15180万
 $69,410/呎
-(16年-04月-14日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
           <t>A | 1320呎 (4+房)
 $4308万
 $32,634/呎
-(16年-05月-08日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -20094,7 +20094,7 @@
           <t>B | 1316呎 (4+房)
 $3998万
 $30,381/呎
-(16年-04月-26日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -20102,7 +20102,7 @@
           <t>C | 2044呎 (3房)
 $12860万
 $62,916/呎
-(20年-02月-20日)</t>
+(20年-02月)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr"/>
@@ -20118,7 +20118,7 @@
           <t>A | 1320呎 (4+房)
 $4295万
 $32,535/呎
-(16年-05月-12日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -20126,7 +20126,7 @@
           <t>B | 1221呎 (4+房)
 $3947万
 $32,325/呎
-(16年-05月-04日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -20134,7 +20134,7 @@
           <t>C | 1723呎 (4+房)
 $7074万
 $41,056/呎
-(16年-04月-27日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -20142,7 +20142,7 @@
           <t>D | 1160呎 (3房)
 $3862万
 $33,292/呎
-(16年-05月-10日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -20157,7 +20157,7 @@
           <t>A | 1320呎 (4+房)
 $4273万
 $32,373/呎
-(16年-05月-11日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -20165,7 +20165,7 @@
           <t>B | 1221呎 (4+房)
 $3896万
 $31,910/呎
-(16年-04月-28日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -20173,7 +20173,7 @@
           <t>C | 1723呎 (4+房)
 $7144万
 $41,465/呎
-(19年-01月-30日)</t>
+(19年-01月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -20181,7 +20181,7 @@
           <t>D | 1160呎 (3房)
 $3841万
 $33,110/呎
-(16年-05月-10日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -20196,7 +20196,7 @@
           <t>A | 1320呎 (4+房)
 $4190万
 $31,739/呎
-(16年-04月-28日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -20204,7 +20204,7 @@
           <t>B | 1316呎 (4+房)
 $7643万
 $58,079/呎
-(16年-04月-14日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -20212,7 +20212,7 @@
           <t>C | 1723呎 (4+房)
 $6358万
 $36,904/呎
-(19年-01月-14日)</t>
+(19年-01月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -20220,7 +20220,7 @@
           <t>D | 1160呎 (3房)
 $3820万
 $32,929/呎
-(16年-05月-11日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -20235,7 +20235,7 @@
           <t>A | 1320呎 (4+房)
 $4196万
 $31,792/呎
-(16年-05月-16日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -20243,7 +20243,7 @@
           <t>B | 1316呎 (4+房)
 $3797万
 $28,851/呎
-(16年-05月-08日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -20251,7 +20251,7 @@
           <t>C | 1723呎 (4+房)
 $5342万
 $31,006/呎
-(24年-06月-23日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -20259,7 +20259,7 @@
           <t>D | 1160呎 (3房)
 $7643万
 $65,889/呎
-(16年-04月-14日)</t>
+(16年-04月)</t>
         </is>
       </c>
     </row>
@@ -20274,7 +20274,7 @@
           <t>A | 1320呎 (4+房)
 $4155万
 $31,477/呎
-(16年-05月-12日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -20282,7 +20282,7 @@
           <t>B | 1316呎 (4+房)
 $3759万
 $28,566/呎
-(16年-05月-08日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -20290,7 +20290,7 @@
           <t>C | 1723呎 (4+房)
 $6268万
 $36,377/呎
-(19年-01月-06日)</t>
+(19年-01月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -20298,7 +20298,7 @@
           <t>D | 1160呎 (3房)
 $3782万
 $32,601/呎
-(16年-05月-17日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -20313,7 +20313,7 @@
           <t>A | 1320呎 (4+房)
 $4011万
 $30,383/呎
-(16年-05月-04日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -20321,7 +20321,7 @@
           <t>B | 1221呎 (4+房)
 $3700万
 $30,303/呎
-(16年-05月-16日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -20329,7 +20329,7 @@
           <t>C | 1723呎 (4+房)
 $6451万
 $37,442/呎
-(19年-01月-16日)</t>
+(19年-01月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -20337,7 +20337,7 @@
           <t>D | 1160呎 (3房)
 $3653万
 $31,491/呎
-(16年-05月-12日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -20352,7 +20352,7 @@
           <t>A | 1320呎 (4+房)
 $3940万
 $29,846/呎
-(16年-05月-05日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -20360,7 +20360,7 @@
           <t>B | 1316呎 (4+房)
 $3653万
 $27,755/呎
-(16年-05月-12日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -20368,7 +20368,7 @@
           <t>C | 1723呎 (4+房)
 $6802万
 $39,477/呎
-(19年-01月-16日)</t>
+(19年-01月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -20376,7 +20376,7 @@
           <t>D | 1160呎 (3房)
 $3540万
 $30,514/呎
-(16年-05月-15日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -20391,7 +20391,7 @@
           <t>A | 1320呎 (4+房)
 $3928万
 $29,756/呎
-(16年-05月-04日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -20399,7 +20399,7 @@
           <t>B | 1316呎 (4+房)
 $3642万
 $27,672/呎
-(16年-05月-16日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -20407,7 +20407,7 @@
           <t>C | 1723呎 (4+房)
 $5814万
 $33,745/呎
-(19年-01月-06日)</t>
+(19年-01月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -20415,7 +20415,7 @@
           <t>D | 1065呎 (3房)
 $3529万
 $33,136/呎
-(16年-05月-12日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -20430,7 +20430,7 @@
           <t>A | 1320呎 (4+房)
 $3837万
 $29,072/呎
-(16年-04月-27日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -20438,7 +20438,7 @@
           <t>B | 1316呎 (4+房)
 $3576万
 $27,174/呎
-(16年-04月-27日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -20446,7 +20446,7 @@
           <t>C | 1723呎 (4+房)
 $5815万
 $33,750/呎
-(19年-01月-16日)</t>
+(19年-01月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -20454,7 +20454,7 @@
           <t>D | 1160呎 (3房)
 $3501万
 $30,179/呎
-(16年-05月-11日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -20469,7 +20469,7 @@
           <t>A | 1320呎 (4+房)
 $3711万
 $28,112/呎
-(16年-04月-26日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -20477,7 +20477,7 @@
           <t>B | 1316呎 (4+房)
 $3512万
 $26,685/呎
-(16年-04月-28日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -20485,7 +20485,7 @@
           <t>C | 1723呎 (4+房)
 $5663万
 $32,869/呎
-(16年-05月-08日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -20493,7 +20493,7 @@
           <t>D | 1160呎 (3房)
 $3403万
 $29,337/呎
-(16年-05月-10日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -20508,7 +20508,7 @@
           <t>A | 1320呎 (4+房)
 $3477万
 $26,341/呎
-(16年-05月-11日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -20516,7 +20516,7 @@
           <t>B | 1221呎 (4+房)
 $3361万
 $27,524/呎
-(16年-04月-14日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -20524,7 +20524,7 @@
           <t>C | 1723呎 (4+房)
 $5448万
 $31,620/呎
-(16年-05月-09日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -20532,7 +20532,7 @@
           <t>D | 1065呎 (3房)
 $3308万
 $31,060/呎
-(16年-05月-11日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -20547,7 +20547,7 @@
           <t>A | 1320呎 (4+房)
 $3317万
 $25,130/呎
-(16年-05月-15日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -20555,7 +20555,7 @@
           <t>B | 1316呎 (4+房)
 $3139万
 $23,852/呎
-(16年-05月-02日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -20563,7 +20563,7 @@
           <t>C | 1723呎 (4+房)
 $5279万
 $30,640/呎
-(16年-05月-19日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -20571,7 +20571,7 @@
           <t>D | 1160呎 (3房)
 $3156万
 $27,204/呎
-(16年-05月-16日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -20586,7 +20586,7 @@
           <t>A | 1320呎 (4+房)
 $3085万
 $23,371/呎
-(16年-05月-09日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -20594,7 +20594,7 @@
           <t>B | 1316呎 (4+房)
 $2919万
 $22,182/呎
-(16年-04月-28日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -20602,7 +20602,7 @@
           <t>C | 1723呎 (4+房)
 $5534万
 $32,120/呎
-(19年-01月-15日)</t>
+(19年-01月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -20610,7 +20610,7 @@
           <t>D | 1065呎 (3房)
 $3045万
 $28,596/呎
-(16年-05月-17日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -20625,7 +20625,7 @@
           <t>A | 1320呎 (4+房)
 $3066万
 $23,230/呎
-(16年-04月-14日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -20633,7 +20633,7 @@
           <t>B | 1316呎 (4+房)
 $2902万
 $22,049/呎
-(16年-04月-27日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -20641,7 +20641,7 @@
           <t>C | 1723呎 (4+房)
 $4871万
 $28,272/呎
-(19年-01月-03日)</t>
+(19年-01月)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -20649,7 +20649,7 @@
           <t>D | 1160呎 (3房)
 $2875万
 $24,784/呎
-(16年-05月-15日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -20664,7 +20664,7 @@
           <t>A | 1320呎 (4+房)
 $2529万
 $19,162/呎
-(16年-05月-18日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -20672,7 +20672,7 @@
           <t>B | 1221呎 (4+房)
 $2211万
 $18,105/呎
-(16年-04月-26日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -20680,7 +20680,7 @@
           <t>C | 1723呎 (4+房)
 $3896万
 $22,610/呎
-(16年-05月-12日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -20688,7 +20688,7 @@
           <t>D | 1160呎 (3房)
 $2329万
 $20,075/呎
-(16年-05月-15日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -20703,7 +20703,7 @@
           <t>A | 1150呎 (4+房)
 $3623万
 $31,505/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -20711,7 +20711,7 @@
           <t>B | 1300呎 (4+房)
 $2506万
 $19,276/呎
-(16年-05月-16日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -20719,7 +20719,7 @@
           <t>C | 1723呎 (3房)
 $3909万
 $22,690/呎
-(16年-05月-15日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -20727,7 +20727,7 @@
           <t>D | 1143呎 (3房)
 $2173万
 $19,011/呎
-(16年-05月-15日)</t>
+(16年-05月)</t>
         </is>
       </c>
     </row>
@@ -20742,7 +20742,7 @@
           <t>A | 1929呎 (3房)
 $4593万
 $23,811/呎
-(16年-04月-07日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -20750,7 +20750,7 @@
           <t>B | 1970呎 (2房)
 $6277万
 $31,865/呎
-(16年-05月-18日)</t>
+(16年-05月)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr"/>

--- a/files/九龙-何文田-天铸 (第2期).xlsx
+++ b/files/九龙-何文田-天铸 (第2期).xlsx
@@ -17696,7 +17696,7 @@
           <t>C | 2503呎 (4+房)
 $8719万
 $34,834/呎
-(16年-04月)</t>
+(16年-04月-07日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr"/>
@@ -17720,7 +17720,7 @@
           <t>B | 2442呎 (4+房)
 $13076万
 $53,546/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -17728,7 +17728,7 @@
           <t>C | 2489呎 (4+房)
 $10247万
 $41,169/呎
-(16年-04月)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr"/>
@@ -17744,7 +17744,7 @@
           <t>A | 1910呎 (4+房)
 $7752万
 $40,584/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -17752,7 +17752,7 @@
           <t>B | 1731呎 (4+房)
 $7478万
 $43,203/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -17760,7 +17760,7 @@
           <t>C | 1154呎 (3房)
 $3469万
 $30,058/呎
-(16年-05月)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -17768,7 +17768,7 @@
           <t>D | 994呎 (3房)
 $2977万
 $29,953/呎
-(16年-05月)</t>
+(16年-05月-08日)</t>
         </is>
       </c>
     </row>
@@ -17783,7 +17783,7 @@
           <t>A | 1910呎 (4+房)
 $8480万
 $44,397/呎
-(19年-04月)</t>
+(19年-04月-03日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -17791,7 +17791,7 @@
           <t>B | 1823呎 (4+房)
 $9466万
 $51,927/呎
-(16年-05月)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -17799,7 +17799,7 @@
           <t>C | 1154呎 (3房)
 $6396万
 $55,425/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -17807,7 +17807,7 @@
           <t>D | 994呎 (3房)
 $6396万
 $64,346/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -17822,7 +17822,7 @@
           <t>A | 1910呎 (4+房)
 $7227万
 $37,837/呎
-(25年-08月)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -17830,7 +17830,7 @@
           <t>B | 1731呎 (4+房)
 $7854万
 $45,373/呎
-(23年-03月)</t>
+(23年-03月-20日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -17838,7 +17838,7 @@
           <t>C | 1154呎 (3房)
 $3377万
 $29,263/呎
-(16年-04月)</t>
+(16年-04月-07日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -17846,7 +17846,7 @@
           <t>D | 994呎 (3房)
 $2968万
 $29,863/呎
-(16年-05月)</t>
+(16年-05月-05日)</t>
         </is>
       </c>
     </row>
@@ -17861,7 +17861,7 @@
           <t>A | 1910呎 (4+房)
 $8610万
 $45,078/呎
-(23年-03月)</t>
+(23年-03月-05日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -17869,7 +17869,7 @@
           <t>B | 1731呎 (4+房)
 $7754万
 $44,794/呎
-(23年-04月)</t>
+(23年-04月-03日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -17877,7 +17877,7 @@
           <t>C | 1154呎 (3房)
 $3364万
 $29,146/呎
-(16年-04月)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -17885,7 +17885,7 @@
           <t>D | 994呎 (3房)
 $2951万
 $29,685/呎
-(16年-05月)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -17900,7 +17900,7 @@
           <t>A | 1910呎 (4+房)
 $8572万
 $44,880/呎
-(23年-03月)</t>
+(23年-03月-02日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -17908,7 +17908,7 @@
           <t>B | 1823呎 (4+房)
 $8529万
 $46,787/呎
-(16年-05月)</t>
+(16年-05月-08日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -17916,7 +17916,7 @@
           <t>C | 1154呎 (3房)
 $3357万
 $29,088/呎
-(16年-05月)</t>
+(16年-05月-15日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -17924,7 +17924,7 @@
           <t>D | 994呎 (3房)
 $2942万
 $29,596/呎
-(16年-05月)</t>
+(16年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -17939,7 +17939,7 @@
           <t>A | 1910呎 (4+房)
 $7672万
 $40,169/呎
-(19年-04月)</t>
+(19年-04月-03日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -17947,7 +17947,7 @@
           <t>B | 1823呎 (4+房)
 $8333万
 $45,711/呎
-(16年-05月)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -17955,7 +17955,7 @@
           <t>C | 1154呎 (3房)
 $3347万
 $29,001/呎
-(16年-05月)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -17963,7 +17963,7 @@
           <t>D | 994呎 (3房)
 $2933万
 $29,507/呎
-(16年-05月)</t>
+(16年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -17978,7 +17978,7 @@
           <t>A | 2019呎 (4+房)
 $8076万
 $40,000/呎
-(19年-09月)</t>
+(19年-09月-22日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -17986,7 +17986,7 @@
           <t>B | 1823呎 (4+房)
 $7295万
 $40,018/呎
-(21年-11月)</t>
+(21年-11月-16日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -17994,7 +17994,7 @@
           <t>C | 1154呎 (3房)
 $3286万
 $28,479/呎
-(16年-05月)</t>
+(16年-05月-02日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -18002,7 +18002,7 @@
           <t>D | 994呎 (3房)
 $2895万
 $29,124/呎
-(16年-05月)</t>
+(16年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -18017,7 +18017,7 @@
           <t>A | 1910呎 (4+房)
 $8087万
 $42,338/呎
-(19年-04月)</t>
+(19年-04月-09日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -18025,7 +18025,7 @@
           <t>B | 1823呎 (4+房)
 $6927万
 $38,000/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -18033,7 +18033,7 @@
           <t>C | 1154呎 (3房)
 $3211万
 $27,824/呎
-(16年-05月)</t>
+(16年-05月-02日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -18041,7 +18041,7 @@
           <t>D | 994呎 (3房)
 $2857万
 $28,745/呎
-(16年-05月)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -18056,7 +18056,7 @@
           <t>A | 2019呎 (4+房)
 $7207万
 $35,698/呎
-(16年-05月)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -18064,7 +18064,7 @@
           <t>B | 1823呎 (4+房)
 $15180万
 $83,269/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -18072,7 +18072,7 @@
           <t>C | 1154呎 (3房)
 $3137万
 $27,184/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -18080,7 +18080,7 @@
           <t>D | 994呎 (3房)
 $2792万
 $28,084/呎
-(16年-05月)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -18095,7 +18095,7 @@
           <t>A | 2019呎 (4+房)
 $5588万
 $27,679/呎
-(16年-04月)</t>
+(16年-04月-25日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -18103,7 +18103,7 @@
           <t>B | 1823呎 (4+房)
 $5001万
 $27,433/呎
-(16年-05月)</t>
+(16年-05月-04日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -18111,7 +18111,7 @@
           <t>C | 1154呎 (3房)
 $3008万
 $26,069/呎
-(16年-04月)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -18119,7 +18119,7 @@
           <t>D | 994呎 (3房)
 $2705万
 $27,213/呎
-(16年-05月)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -18134,7 +18134,7 @@
           <t>A | 1910呎 (4+房)
 $5588万
 $29,257/呎
-(16年-05月)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -18142,7 +18142,7 @@
           <t>B | 1823呎 (4+房)
 $5001万
 $27,435/呎
-(16年-05月)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -18150,7 +18150,7 @@
           <t>C | 1154呎 (3房)
 $2858万
 $24,766/呎
-(16年-05月)</t>
+(16年-05月-05日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -18158,7 +18158,7 @@
           <t>D | 994呎 (3房)
 $2637万
 $26,533/呎
-(16年-05月)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -18173,7 +18173,7 @@
           <t>A | 2019呎 (4+房)
 $4703万
 $23,292/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -18181,7 +18181,7 @@
           <t>B | 1823呎 (4+房)
 $4234万
 $23,227/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -18189,7 +18189,7 @@
           <t>C | 1154呎 (3房)
 $2741万
 $23,751/呎
-(16年-04月)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -18197,7 +18197,7 @@
           <t>D | 994呎 (3房)
 $2529万
 $25,445/呎
-(16年-05月)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -18212,7 +18212,7 @@
           <t>A | 2019呎 (4+房)
 $6379万
 $31,596/呎
-(16年-03月)</t>
+(16年-03月-31日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -18220,7 +18220,7 @@
           <t>B | 1823呎 (4+房)
 $6379万
 $34,993/呎
-(16年-03月)</t>
+(16年-03月-31日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -18228,7 +18228,7 @@
           <t>C | 1154呎 (3房)
 $2289万
 $19,832/呎
-(16年-05月)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -18236,7 +18236,7 @@
           <t>D | 994呎 (3房)
 $2036万
 $20,483/呎
-(16年-05月)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -18251,7 +18251,7 @@
           <t>A | 2019呎 (4+房)
 $3613万
 $17,895/呎
-(16年-04月)</t>
+(16年-04月-18日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -18259,7 +18259,7 @@
           <t>B | 1807呎 (4+房)
 $3006万
 $16,637/呎
-(16年-05月)</t>
+(16年-05月-08日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -18267,7 +18267,7 @@
           <t>C | 1045呎 (3房)
 $2070万
 $19,812/呎
-(16年-04月)</t>
+(16年-04月-24日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -18275,7 +18275,7 @@
           <t>D | 863呎 (3房)
 $1833万
 $21,235/呎
-(16年-05月)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -18290,7 +18290,7 @@
           <t>A | 2065呎 (3房)
 $4674万
 $22,634/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -18298,7 +18298,7 @@
           <t>B | 2337呎 (4+房)
 $5436万
 $23,262/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr"/>
@@ -18438,7 +18438,7 @@
           <t>A | 2681呎 (4+房)
 $14831万
 $55,319/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -18447,7 +18447,7 @@
           <t>C | 2079呎 (3房)
 $7509万
 $36,121/呎
-(16年-04月)</t>
+(16年-04月-25日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -18455,7 +18455,7 @@
           <t>D | 2090呎 (3房)
 $7751万
 $37,088/呎
-(16年-05月)</t>
+(16年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -18472,7 +18472,7 @@
           <t>C | 2026呎 (4+房)
 $8348万
 $41,206/呎
-(16年-05月)</t>
+(16年-05月-10日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr"/>
@@ -18480,52 +18480,52 @@
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
+          <t>22&amp;23</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 2199呎 (4+房)
+$11391万
+$51,801/呎
+(24年-04月-28日)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 2361呎 (4+房)
+$12169万
+$51,540/呎
+(16年-04月-21日)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr"/>
+      <c r="C8" s="21" t="inlineStr"/>
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 1428呎 (4+房)
 $4207万
 $29,461/呎
-(16年-04月)</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr">
+(16年-04月-19日)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 1237呎 (3房)
 $3534万
 $28,573/呎
-(16年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>22&amp;23</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>A | 2199呎 (4+房)
-$11391万
-$51,801/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>B | 2361呎 (4+房)
-$12169万
-$51,540/呎
-(16年-04月)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr"/>
-      <c r="E8" s="21" t="inlineStr"/>
+(16年-04月-19日)</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -18538,7 +18538,7 @@
           <t>A | 1738呎 (4+房)
 $7820万
 $44,994/呎
-(16年-05月)</t>
+(16年-05月-05日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -18546,7 +18546,7 @@
           <t>B | 1606呎 (4+房)
 $7198万
 $44,819/呎
-(16年-04月)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -18554,7 +18554,7 @@
           <t>C | 1428呎 (4+房)
 $4194万
 $29,373/呎
-(16年-04月)</t>
+(16年-04月-17日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -18562,7 +18562,7 @@
           <t>D | 1237呎 (3房)
 $3527万
 $28,516/呎
-(16年-04月)</t>
+(16年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -18577,7 +18577,7 @@
           <t>A | 1646呎 (4+房)
 $8182万
 $49,711/呎
-(19年-01月)</t>
+(19年-01月-27日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -18585,7 +18585,7 @@
           <t>B | 1606呎 (4+房)
 $7464万
 $46,475/呎
-(19年-03月)</t>
+(19年-03月-03日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -18593,7 +18593,7 @@
           <t>C | 1428呎 (4+房)
 $8351万
 $58,483/呎
-(16年-03月)</t>
+(16年-03月-24日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -18601,7 +18601,7 @@
           <t>D | 1237呎 (3房)
 $3520万
 $28,459/呎
-(16年-04月)</t>
+(16年-04月-12日)</t>
         </is>
       </c>
     </row>
@@ -18616,7 +18616,7 @@
           <t>A | 1738呎 (4+房)
 $7583万
 $43,633/呎
-(16年-04月)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -18624,7 +18624,7 @@
           <t>B | 1708呎 (4+房)
 $6946万
 $40,665/呎
-(16年-05月)</t>
+(16年-05月-08日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -18632,7 +18632,7 @@
           <t>C | 1428呎 (4+房)
 $8351万
 $58,483/呎
-(16年-03月)</t>
+(16年-03月-24日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -18640,7 +18640,7 @@
           <t>D | 1237呎 (3房)
 $3513万
 $28,402/呎
-(16年-04月)</t>
+(16年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -18655,7 +18655,7 @@
           <t>A | 1646呎 (4+房)
 $6398万
 $38,870/呎
-(24年-10月)</t>
+(24年-10月-14日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -18663,7 +18663,7 @@
           <t>B | 1606呎 (4+房)
 $7068万
 $44,010/呎
-(26年-01月)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -18671,7 +18671,7 @@
           <t>C | 1428呎 (4+房)
 $4169万
 $29,198/呎
-(16年-04月)</t>
+(16年-04月-17日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -18679,7 +18679,7 @@
           <t>D | 1237呎 (3房)
 $3513万
 $28,402/呎
-(16年-04月)</t>
+(16年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -18694,7 +18694,7 @@
           <t>A | 1738呎 (4+房)
 $7318万
 $42,104/呎
-(16年-04月)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -18702,7 +18702,7 @@
           <t>B | 1708呎 (4+房)
 $6735万
 $39,433/呎
-(16年-05月)</t>
+(16年-05月-11日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -18710,7 +18710,7 @@
           <t>C | 1428呎 (4+房)
 $4145万
 $29,024/呎
-(16年-04月)</t>
+(16年-04月-17日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -18718,7 +18718,7 @@
           <t>D | 1237呎 (3房)
 $3499万
 $28,289/呎
-(16年-04月)</t>
+(16年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -18733,7 +18733,7 @@
           <t>A | 1738呎 (4+房)
 $7188万
 $41,360/呎
-(16年-04月)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -18741,7 +18741,7 @@
           <t>B | 1708呎 (4+房)
 $6649万
 $38,927/呎
-(16年-04月)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -18749,7 +18749,7 @@
           <t>C | 1428呎 (4+房)
 $4132万
 $28,937/呎
-(16年-04月)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -18757,7 +18757,7 @@
           <t>D | 1237呎 (3房)
 $3492万
 $28,233/呎
-(16年-04月)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
     </row>
@@ -18772,7 +18772,7 @@
           <t>A | 1646呎 (4+房)
 $7911万
 $48,062/呎
-(19年-02月)</t>
+(19年-02月-17日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -18780,7 +18780,7 @@
           <t>B | 1606呎 (4+房)
 $6829万
 $42,522/呎
-(19年-08月)</t>
+(19年-08月-06日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -18788,7 +18788,7 @@
           <t>C | 1428呎 (4+房)
 $8145万
 $57,036/呎
-(16年-03月)</t>
+(16年-03月-24日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -18796,7 +18796,7 @@
           <t>D | 1142呎 (3房)
 $3482万
 $30,490/呎
-(16年-04月)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
     </row>
@@ -18811,7 +18811,7 @@
           <t>A | 1738呎 (4+房)
 $6652万
 $38,276/呎
-(16年-05月)</t>
+(16年-05月-22日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -18819,7 +18819,7 @@
           <t>B | 1708呎 (4+房)
 $6410万
 $37,530/呎
-(16年-04月)</t>
+(16年-04月-18日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -18827,7 +18827,7 @@
           <t>C | 1428呎 (4+房)
 $8145万
 $57,036/呎
-(16年-03月)</t>
+(16年-03月-24日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -18835,7 +18835,7 @@
           <t>D | 1142呎 (3房)
 $3419万
 $29,941/呎
-(16年-04月)</t>
+(16年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -18850,7 +18850,7 @@
           <t>A | 1738呎 (4+房)
 $6167万
 $35,482/呎
-(16年-04月)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -18858,7 +18858,7 @@
           <t>B | 1708呎 (4+房)
 $5942万
 $34,790/呎
-(16年-04月)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -18866,7 +18866,7 @@
           <t>C | 1428呎 (4+房)
 $3892万
 $27,256/呎
-(16年-05月)</t>
+(16年-05月-10日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -18874,7 +18874,7 @@
           <t>D | 1237呎 (3房)
 $3306万
 $26,729/呎
-(16年-05月)</t>
+(16年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
           <t>A | 1738呎 (4+房)
 $5080万
 $29,231/呎
-(16年-04月)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -18897,7 +18897,7 @@
           <t>B | 1708呎 (4+房)
 $4914万
 $28,771/呎
-(16年-04月)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -18905,7 +18905,7 @@
           <t>C | 1428呎 (4+房)
 $3764万
 $26,357/呎
-(16年-04月)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -18913,7 +18913,7 @@
           <t>D | 1237呎 (3房)
 $3197万
 $25,847/呎
-(16年-04月)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -18928,7 +18928,7 @@
           <t>A | 1738呎 (4+房)
 $4288万
 $24,671/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -18936,7 +18936,7 @@
           <t>B | 1708呎 (4+房)
 $4197万
 $24,571/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -18944,7 +18944,7 @@
           <t>C | 1428呎 (4+房)
 $3666万
 $25,672/呎
-(16年-04月)</t>
+(16年-04月-13日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -18952,7 +18952,7 @@
           <t>D | 1237呎 (3房)
 $3114万
 $25,175/呎
-(16年-04月)</t>
+(16年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -18967,7 +18967,7 @@
           <t>A | 1738呎 (4+房)
 $4159万
 $23,931/呎
-(16年-04月)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -18975,7 +18975,7 @@
           <t>B | 1708呎 (4+房)
 $4071万
 $23,833/呎
-(16年-04月)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -18983,7 +18983,7 @@
           <t>C | 1428呎 (4+房)
 $3593万
 $25,158/呎
-(16年-05月)</t>
+(16年-05月-04日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -18991,7 +18991,7 @@
           <t>D | 1237呎 (3房)
 $3036万
 $24,546/呎
-(16年-04月)</t>
+(16年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -19006,7 +19006,7 @@
           <t>A | 1738呎 (4+房)
 $3989万
 $22,950/呎
-(16年-04月)</t>
+(16年-04月-18日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -19014,7 +19014,7 @@
           <t>B | 1708呎 (4+房)
 $3904万
 $22,856/呎
-(16年-04月)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -19022,7 +19022,7 @@
           <t>C | 1428呎 (4+房)
 $3409万
 $23,875/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -19030,7 +19030,7 @@
           <t>D | 1237呎 (3房)
 $2881万
 $23,294/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -19045,7 +19045,7 @@
           <t>A | 1738呎 (4+房)
 $3206万
 $18,449/呎
-(16年-05月)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -19053,7 +19053,7 @@
           <t>B | 1708呎 (4+房)
 $2903万
 $16,996/呎
-(16年-04月)</t>
+(16年-04月-18日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -19061,7 +19061,7 @@
           <t>C | 1428呎 (4+房)
 $2617万
 $18,328/呎
-(16年-05月)</t>
+(16年-05月-05日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -19069,7 +19069,7 @@
           <t>D | 1237呎 (3房)
 $2320万
 $18,752/呎
-(16年-05月)</t>
+(16年-05月-08日)</t>
         </is>
       </c>
     </row>
@@ -19084,7 +19084,7 @@
           <t>A | 1630呎 (4+房)
 $3503万
 $21,490/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -19092,7 +19092,7 @@
           <t>B | 1691呎 (4+房)
 $2905万
 $17,177/呎
-(16年-04月)</t>
+(16年-04月-18日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -19100,7 +19100,7 @@
           <t>C | 1324呎 (4+房)
 $2597万
 $19,615/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -19108,7 +19108,7 @@
           <t>D | 1221呎 (3房)
 $2113万
 $17,309/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -19246,7 +19246,7 @@
           <t>A | 2681呎 (4+房)
 $15227万
 $56,795/呎
-(25年-11月)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -19255,7 +19255,7 @@
           <t>C | 1990呎 (3房)
 $12540万
 $63,015/呎
-(19年-11月)</t>
+(19年-11月-03日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -19263,7 +19263,7 @@
           <t>D | 2173呎 (3房)
 $7670万
 $35,298/呎
-(16年-05月)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -19280,7 +19280,7 @@
           <t>C | 2128呎 (3房)
 $8248万
 $38,761/呎
-(16年-05月)</t>
+(16年-05月-15日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr"/>
@@ -19288,52 +19288,52 @@
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
+          <t>22&amp;23</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 2265呎 (4+房)
+$15583万
+$68,797/呎
+(19年-07月-29日)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 2199呎 (4+房)
+$14260万
+$64,849/呎
+(19年-02月-20日)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr"/>
+      <c r="C8" s="21" t="inlineStr"/>
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 1237呎 (3房)
 $3250万
 $26,273/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr">
+(24年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 1428呎 (4+房)
 $4251万
 $29,770/呎
-(16年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>22&amp;23</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>A | 2265呎 (4+房)
-$15583万
-$68,797/呎
-(19年-07月)</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>B | 2199呎 (4+房)
-$14260万
-$64,849/呎
-(19年-02月)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr"/>
-      <c r="E8" s="21" t="inlineStr"/>
+(16年-04月-26日)</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -19346,7 +19346,7 @@
           <t>A | 1708呎 (4+房)
 $7567万
 $44,304/呎
-(19年-02月)</t>
+(19年-02月-25日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -19354,7 +19354,7 @@
           <t>B | 1738呎 (4+房)
 $6650万
 $38,262/呎
-(16年-04月)</t>
+(16年-04月-24日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -19362,7 +19362,7 @@
           <t>C | 1237呎 (3房)
 $7133万
 $57,666/呎
-(16年-03月)</t>
+(16年-03月-31日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -19370,7 +19370,7 @@
           <t>D | 1428呎 (4+房)
 $4238万
 $29,681/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -19385,7 +19385,7 @@
           <t>A | 1708呎 (4+房)
 $7472万
 $43,746/呎
-(19年-01月)</t>
+(19年-01月-30日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -19393,7 +19393,7 @@
           <t>B | 1738呎 (4+房)
 $6532万
 $37,585/呎
-(16年-05月)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -19401,7 +19401,7 @@
           <t>C | 1237呎 (3房)
 $3556万
 $28,747/呎
-(16年-04月)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -19409,7 +19409,7 @@
           <t>D | 1428呎 (4+房)
 $4226万
 $29,592/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -19424,7 +19424,7 @@
           <t>A | 1708呎 (4+房)
 $6764万
 $39,600/呎
-(19年-01月)</t>
+(19年-01月-24日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -19432,7 +19432,7 @@
           <t>B | 1738呎 (4+房)
 $6417万
 $36,921/呎
-(16年-05月)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -19440,7 +19440,7 @@
           <t>C | 1237呎 (3房)
 $3549万
 $28,689/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -19448,7 +19448,7 @@
           <t>D | 1428呎 (4+房)
 $4213万
 $29,503/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -19463,7 +19463,7 @@
           <t>A | 1708呎 (4+房)
 $13498万
 $79,030/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -19471,7 +19471,7 @@
           <t>B | 1738呎 (4+房)
 $13498万
 $77,666/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -19479,7 +19479,7 @@
           <t>C | 1237呎 (3房)
 $3549万
 $28,689/呎
-(16年-05月)</t>
+(16年-05月-03日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -19487,7 +19487,7 @@
           <t>D | 1428呎 (4+房)
 $4213万
 $29,503/呎
-(16年-05月)</t>
+(16年-05月-08日)</t>
         </is>
       </c>
     </row>
@@ -19502,7 +19502,7 @@
           <t>A | 1708呎 (4+房)
 $6662万
 $39,006/呎
-(23年-05月)</t>
+(23年-05月-04日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -19510,7 +19510,7 @@
           <t>B | 1738呎 (4+房)
 $6192万
 $35,627/呎
-(16年-04月)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -19518,7 +19518,7 @@
           <t>C | 1237呎 (3房)
 $3535万
 $28,575/呎
-(16年-04月)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -19526,7 +19526,7 @@
           <t>D | 1428呎 (4+房)
 $4188万
 $29,328/呎
-(16年-04月)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -19541,7 +19541,7 @@
           <t>A | 1708呎 (4+房)
 $6663万
 $39,009/呎
-(19年-01月)</t>
+(19年-01月-20日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -19549,7 +19549,7 @@
           <t>B | 1738呎 (4+房)
 $6082万
 $34,997/呎
-(16年-05月)</t>
+(16年-05月-15日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -19557,7 +19557,7 @@
           <t>C | 1237呎 (3房)
 $3528万
 $28,518/呎
-(16年-04月)</t>
+(16年-04月-25日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -19565,7 +19565,7 @@
           <t>D | 1428呎 (4+房)
 $4175万
 $29,240/呎
-(16年-04月)</t>
+(16年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -19580,7 +19580,7 @@
           <t>A | 1708呎 (4+房)
 $6483万
 $37,957/呎
-(19年-01月)</t>
+(19年-01月-17日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -19588,7 +19588,7 @@
           <t>B | 1738呎 (4+房)
 $6064万
 $34,892/呎
-(16年-04月)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -19596,7 +19596,7 @@
           <t>C | 1237呎 (3房)
 $3517万
 $28,432/呎
-(16年-04月)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -19604,7 +19604,7 @@
           <t>D | 1428呎 (4+房)
 $4163万
 $29,152/呎
-(16年-05月)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -19619,7 +19619,7 @@
           <t>A | 1708呎 (4+房)
 $6290万
 $36,827/呎
-(16年-05月)</t>
+(16年-05月-08日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -19627,7 +19627,7 @@
           <t>B | 1738呎 (4+房)
 $5864万
 $33,740/呎
-(16年-04月)</t>
+(16年-04月-24日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -19635,7 +19635,7 @@
           <t>C | 1237呎 (3房)
 $3454万
 $27,921/呎
-(16年-05月)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -19643,7 +19643,7 @@
           <t>D | 1428呎 (4+房)
 $4067万
 $28,482/呎
-(16年-04月)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -19658,7 +19658,7 @@
           <t>A | 1708呎 (4+房)
 $5890万
 $34,483/呎
-(19年-01月)</t>
+(19年-01月-21日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -19666,7 +19666,7 @@
           <t>B | 1738呎 (4+房)
 $5436万
 $31,277/呎
-(16年-04月)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -19674,7 +19674,7 @@
           <t>C | 1237呎 (3房)
 $3340万
 $26,999/呎
-(16年-05月)</t>
+(16年-05月-04日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -19682,7 +19682,7 @@
           <t>D | 1428呎 (4+房)
 $3933万
 $27,542/呎
-(16年-05月)</t>
+(16年-05月-04日)</t>
         </is>
       </c>
     </row>
@@ -19697,7 +19697,7 @@
           <t>A | 1708呎 (4+房)
 $5567万
 $32,593/呎
-(19年-03月)</t>
+(19年-03月-03日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -19705,7 +19705,7 @@
           <t>B | 1738呎 (4+房)
 $4441万
 $25,554/呎
-(16年-05月)</t>
+(16年-05月-02日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -19713,7 +19713,7 @@
           <t>C | 1237呎 (3房)
 $3263万
 $26,378/呎
-(16年-04月)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -19721,7 +19721,7 @@
           <t>D | 1428呎 (4+房)
 $3842万
 $26,908/呎
-(16年-04月)</t>
+(16年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -19736,7 +19736,7 @@
           <t>A | 1708呎 (4+房)
 $8063万
 $47,206/呎
-(16年-03月)</t>
+(16年-03月-31日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -19744,7 +19744,7 @@
           <t>B | 1738呎 (4+房)
 $8063万
 $46,391/呎
-(16年-03月)</t>
+(16年-03月-31日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -19752,7 +19752,7 @@
           <t>C | 1237呎 (3房)
 $3178万
 $25,692/呎
-(16年-04月)</t>
+(16年-04月-25日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -19760,7 +19760,7 @@
           <t>D | 1428呎 (4+房)
 $3743万
 $26,209/呎
-(16年-04月)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -19775,7 +19775,7 @@
           <t>A | 1708呎 (4+房)
 $5332万
 $31,220/呎
-(19年-01月)</t>
+(19年-01月-31日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -19783,7 +19783,7 @@
           <t>B | 1738呎 (4+房)
 $3891万
 $22,388/呎
-(16年-04月)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -19791,7 +19791,7 @@
           <t>C | 1237呎 (3房)
 $3115万
 $25,179/呎
-(16年-04月)</t>
+(16年-04月-24日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -19799,7 +19799,7 @@
           <t>D | 1428呎 (4+房)
 $3630万
 $25,422/呎
-(16年-04月)</t>
+(16年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -19814,7 +19814,7 @@
           <t>A | 1708呎 (4+房)
 $5188万
 $30,378/呎
-(19年-01月)</t>
+(19年-01月-10日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -19822,7 +19822,7 @@
           <t>B | 1738呎 (4+房)
 $3790万
 $21,806/呎
-(16年-04月)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -19830,7 +19830,7 @@
           <t>C | 1237呎 (3房)
 $2800万
 $22,635/呎
-(16年-04月)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -19838,7 +19838,7 @@
           <t>D | 1428呎 (4+房)
 $3227万
 $22,600/呎
-(16年-04月)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
     </row>
@@ -19853,7 +19853,7 @@
           <t>A | 1708呎 (4+房)
 $5049万
 $29,560/呎
-(19年-01月)</t>
+(19年-01月-14日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -19861,7 +19861,7 @@
           <t>B | 1738呎 (4+房)
 $3127万
 $17,990/呎
-(16年-04月)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -19869,7 +19869,7 @@
           <t>C | 1237呎 (3房)
 $2082万
 $16,831/呎
-(16年-04月)</t>
+(16年-04月-18日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -19877,7 +19877,7 @@
           <t>D | 1428呎 (4+房)
 $2499万
 $17,500/呎
-(16年-04月)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
     </row>
@@ -19892,7 +19892,7 @@
           <t>A | 1691呎 (4+房)
 $3166万
 $18,724/呎
-(16年-05月)</t>
+(16年-05月-03日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -19900,7 +19900,7 @@
           <t>B | 1722呎 (4+房)
 $3061万
 $17,778/呎
-(16年-05月)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -19908,7 +19908,7 @@
           <t>C | 1221呎 (3房)
 $2198万
 $18,005/呎
-(16年-04月)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -19916,7 +19916,7 @@
           <t>D | 1412呎 (4+房)
 $2421万
 $17,145/呎
-(16年-04月)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
           <t>A | 2733呎 (4+房)
 $21391万
 $78,270/呎
-(19年-02月)</t>
+(19年-02月-14日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -20063,7 +20063,7 @@
           <t>C | 2130呎 (4+房)
 $9165万
 $43,028/呎
-(16年-04月)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -20071,7 +20071,7 @@
           <t>D | 2187呎 (4+房)
 $15180万
 $69,410/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
           <t>A | 1320呎 (4+房)
 $4308万
 $32,634/呎
-(16年-05月)</t>
+(16年-05月-08日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -20094,7 +20094,7 @@
           <t>B | 1316呎 (4+房)
 $3998万
 $30,381/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -20102,7 +20102,7 @@
           <t>C | 2044呎 (3房)
 $12860万
 $62,916/呎
-(20年-02月)</t>
+(20年-02月-20日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr"/>
@@ -20118,7 +20118,7 @@
           <t>A | 1320呎 (4+房)
 $4295万
 $32,535/呎
-(16年-05月)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -20126,7 +20126,7 @@
           <t>B | 1221呎 (4+房)
 $3947万
 $32,325/呎
-(16年-05月)</t>
+(16年-05月-04日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -20134,7 +20134,7 @@
           <t>C | 1723呎 (4+房)
 $7074万
 $41,056/呎
-(16年-04月)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -20142,7 +20142,7 @@
           <t>D | 1160呎 (3房)
 $3862万
 $33,292/呎
-(16年-05月)</t>
+(16年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -20157,7 +20157,7 @@
           <t>A | 1320呎 (4+房)
 $4273万
 $32,373/呎
-(16年-05月)</t>
+(16年-05月-11日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -20165,7 +20165,7 @@
           <t>B | 1221呎 (4+房)
 $3896万
 $31,910/呎
-(16年-04月)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -20173,7 +20173,7 @@
           <t>C | 1723呎 (4+房)
 $7144万
 $41,465/呎
-(19年-01月)</t>
+(19年-01月-30日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -20181,7 +20181,7 @@
           <t>D | 1160呎 (3房)
 $3841万
 $33,110/呎
-(16年-05月)</t>
+(16年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -20196,7 +20196,7 @@
           <t>A | 1320呎 (4+房)
 $4190万
 $31,739/呎
-(16年-04月)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -20204,7 +20204,7 @@
           <t>B | 1316呎 (4+房)
 $7643万
 $58,079/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -20212,7 +20212,7 @@
           <t>C | 1723呎 (4+房)
 $6358万
 $36,904/呎
-(19年-01月)</t>
+(19年-01月-14日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -20220,7 +20220,7 @@
           <t>D | 1160呎 (3房)
 $3820万
 $32,929/呎
-(16年-05月)</t>
+(16年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -20235,7 +20235,7 @@
           <t>A | 1320呎 (4+房)
 $4196万
 $31,792/呎
-(16年-05月)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -20243,7 +20243,7 @@
           <t>B | 1316呎 (4+房)
 $3797万
 $28,851/呎
-(16年-05月)</t>
+(16年-05月-08日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -20251,7 +20251,7 @@
           <t>C | 1723呎 (4+房)
 $5342万
 $31,006/呎
-(24年-06月)</t>
+(24年-06月-23日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -20259,7 +20259,7 @@
           <t>D | 1160呎 (3房)
 $7643万
 $65,889/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -20274,7 +20274,7 @@
           <t>A | 1320呎 (4+房)
 $4155万
 $31,477/呎
-(16年-05月)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -20282,7 +20282,7 @@
           <t>B | 1316呎 (4+房)
 $3759万
 $28,566/呎
-(16年-05月)</t>
+(16年-05月-08日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -20290,7 +20290,7 @@
           <t>C | 1723呎 (4+房)
 $6268万
 $36,377/呎
-(19年-01月)</t>
+(19年-01月-06日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -20298,7 +20298,7 @@
           <t>D | 1160呎 (3房)
 $3782万
 $32,601/呎
-(16年-05月)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -20313,7 +20313,7 @@
           <t>A | 1320呎 (4+房)
 $4011万
 $30,383/呎
-(16年-05月)</t>
+(16年-05月-04日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -20321,7 +20321,7 @@
           <t>B | 1221呎 (4+房)
 $3700万
 $30,303/呎
-(16年-05月)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -20329,7 +20329,7 @@
           <t>C | 1723呎 (4+房)
 $6451万
 $37,442/呎
-(19年-01月)</t>
+(19年-01月-16日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -20337,7 +20337,7 @@
           <t>D | 1160呎 (3房)
 $3653万
 $31,491/呎
-(16年-05月)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -20352,7 +20352,7 @@
           <t>A | 1320呎 (4+房)
 $3940万
 $29,846/呎
-(16年-05月)</t>
+(16年-05月-05日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -20360,7 +20360,7 @@
           <t>B | 1316呎 (4+房)
 $3653万
 $27,755/呎
-(16年-05月)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -20368,7 +20368,7 @@
           <t>C | 1723呎 (4+房)
 $6802万
 $39,477/呎
-(19年-01月)</t>
+(19年-01月-16日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -20376,7 +20376,7 @@
           <t>D | 1160呎 (3房)
 $3540万
 $30,514/呎
-(16年-05月)</t>
+(16年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -20391,7 +20391,7 @@
           <t>A | 1320呎 (4+房)
 $3928万
 $29,756/呎
-(16年-05月)</t>
+(16年-05月-04日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -20399,7 +20399,7 @@
           <t>B | 1316呎 (4+房)
 $3642万
 $27,672/呎
-(16年-05月)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -20407,7 +20407,7 @@
           <t>C | 1723呎 (4+房)
 $5814万
 $33,745/呎
-(19年-01月)</t>
+(19年-01月-06日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -20415,7 +20415,7 @@
           <t>D | 1065呎 (3房)
 $3529万
 $33,136/呎
-(16年-05月)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -20430,7 +20430,7 @@
           <t>A | 1320呎 (4+房)
 $3837万
 $29,072/呎
-(16年-04月)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -20438,7 +20438,7 @@
           <t>B | 1316呎 (4+房)
 $3576万
 $27,174/呎
-(16年-04月)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -20446,7 +20446,7 @@
           <t>C | 1723呎 (4+房)
 $5815万
 $33,750/呎
-(19年-01月)</t>
+(19年-01月-16日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -20454,7 +20454,7 @@
           <t>D | 1160呎 (3房)
 $3501万
 $30,179/呎
-(16年-05月)</t>
+(16年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -20469,7 +20469,7 @@
           <t>A | 1320呎 (4+房)
 $3711万
 $28,112/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -20477,7 +20477,7 @@
           <t>B | 1316呎 (4+房)
 $3512万
 $26,685/呎
-(16年-04月)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -20485,7 +20485,7 @@
           <t>C | 1723呎 (4+房)
 $5663万
 $32,869/呎
-(16年-05月)</t>
+(16年-05月-08日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -20493,7 +20493,7 @@
           <t>D | 1160呎 (3房)
 $3403万
 $29,337/呎
-(16年-05月)</t>
+(16年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -20508,7 +20508,7 @@
           <t>A | 1320呎 (4+房)
 $3477万
 $26,341/呎
-(16年-05月)</t>
+(16年-05月-11日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -20516,7 +20516,7 @@
           <t>B | 1221呎 (4+房)
 $3361万
 $27,524/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -20524,7 +20524,7 @@
           <t>C | 1723呎 (4+房)
 $5448万
 $31,620/呎
-(16年-05月)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -20532,7 +20532,7 @@
           <t>D | 1065呎 (3房)
 $3308万
 $31,060/呎
-(16年-05月)</t>
+(16年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -20547,7 +20547,7 @@
           <t>A | 1320呎 (4+房)
 $3317万
 $25,130/呎
-(16年-05月)</t>
+(16年-05月-15日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -20555,7 +20555,7 @@
           <t>B | 1316呎 (4+房)
 $3139万
 $23,852/呎
-(16年-05月)</t>
+(16年-05月-02日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -20563,7 +20563,7 @@
           <t>C | 1723呎 (4+房)
 $5279万
 $30,640/呎
-(16年-05月)</t>
+(16年-05月-19日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -20571,7 +20571,7 @@
           <t>D | 1160呎 (3房)
 $3156万
 $27,204/呎
-(16年-05月)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -20586,7 +20586,7 @@
           <t>A | 1320呎 (4+房)
 $3085万
 $23,371/呎
-(16年-05月)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -20594,7 +20594,7 @@
           <t>B | 1316呎 (4+房)
 $2919万
 $22,182/呎
-(16年-04月)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -20602,7 +20602,7 @@
           <t>C | 1723呎 (4+房)
 $5534万
 $32,120/呎
-(19年-01月)</t>
+(19年-01月-15日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -20610,7 +20610,7 @@
           <t>D | 1065呎 (3房)
 $3045万
 $28,596/呎
-(16年-05月)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -20625,7 +20625,7 @@
           <t>A | 1320呎 (4+房)
 $3066万
 $23,230/呎
-(16年-04月)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -20633,7 +20633,7 @@
           <t>B | 1316呎 (4+房)
 $2902万
 $22,049/呎
-(16年-04月)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -20641,7 +20641,7 @@
           <t>C | 1723呎 (4+房)
 $4871万
 $28,272/呎
-(19年-01月)</t>
+(19年-01月-03日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -20649,7 +20649,7 @@
           <t>D | 1160呎 (3房)
 $2875万
 $24,784/呎
-(16年-05月)</t>
+(16年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -20664,7 +20664,7 @@
           <t>A | 1320呎 (4+房)
 $2529万
 $19,162/呎
-(16年-05月)</t>
+(16年-05月-18日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -20672,7 +20672,7 @@
           <t>B | 1221呎 (4+房)
 $2211万
 $18,105/呎
-(16年-04月)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -20680,7 +20680,7 @@
           <t>C | 1723呎 (4+房)
 $3896万
 $22,610/呎
-(16年-05月)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -20688,7 +20688,7 @@
           <t>D | 1160呎 (3房)
 $2329万
 $20,075/呎
-(16年-05月)</t>
+(16年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -20703,7 +20703,7 @@
           <t>A | 1150呎 (4+房)
 $3623万
 $31,505/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -20711,7 +20711,7 @@
           <t>B | 1300呎 (4+房)
 $2506万
 $19,276/呎
-(16年-05月)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -20719,7 +20719,7 @@
           <t>C | 1723呎 (3房)
 $3909万
 $22,690/呎
-(16年-05月)</t>
+(16年-05月-15日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -20727,7 +20727,7 @@
           <t>D | 1143呎 (3房)
 $2173万
 $19,011/呎
-(16年-05月)</t>
+(16年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -20742,7 +20742,7 @@
           <t>A | 1929呎 (3房)
 $4593万
 $23,811/呎
-(16年-04月)</t>
+(16年-04月-07日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -20750,7 +20750,7 @@
           <t>B | 1970呎 (2房)
 $6277万
 $31,865/呎
-(16年-05月)</t>
+(16年-05月-18日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr"/>
